--- a/lessons/gallery/excels/remarks_ideal.xlsx
+++ b/lessons/gallery/excels/remarks_ideal.xlsx
@@ -162,12 +162,12 @@
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>-Tab (12:31:12.499), +tab (00:00:00)</t>
+        <t>-Tab (12:31:12.499) ~0.67, +tab (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:35:33.317), -Karelia (12:46:59.354), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066), -36 (13:30:50.077), -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881), -` (13:31:57.168), -` (13:32:14.220), -; (13:33:31.713), -August (13:33:55.549), -Wednesday (13:36:38.686), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736), +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
+        <t>-Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.90, -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881) ~0.75, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -; (13:33:31.713), -August (13:33:55.549) ~0.83, -Wednesday (13:36:38.686) ~0.89, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736) ~0.83, +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -187,12 +187,12 @@
     </comment>
     <comment ref="M5" authorId="0" shapeId="0">
       <text>
-        <t>-JavaScript (12:24:24.306), +Javascript (00:00:00)</t>
+        <t>-JavaScript (12:24:24.306) ~0.90, +Javascript (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O5" authorId="0" shapeId="0">
       <text>
-        <t>-myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -Karelia (12:46:59.354), -Karelia (13:28:16.030), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
+        <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -Karelia (12:46:59.354) ~0.86, -Karelia (13:28:16.030) ~0.86, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D12" authorId="0" shapeId="0">
@@ -217,12 +217,12 @@
     </comment>
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
-        <t>-abbreviations (12:29:01.416), +abbreaviations (00:00:00)</t>
+        <t>-abbreviations (12:29:01.416) ~0.93, +abbreaviations (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:35:33.317), -Max (13:05:08.613), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560), -Date (13:33:53.451), -August (13:33:55.549), +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
+        <t>-Karelia (12:35:33.317) ~0.86, -Max (13:05:08.613) ~0.67, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560) ~0.86, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -242,12 +242,12 @@
     </comment>
     <comment ref="M19" authorId="0" shapeId="0">
       <text>
-        <t>-! (12:24:11.928), -boilerplate (12:30:45.202), +boilerpate (00:00:00)</t>
+        <t>-! (12:24:11.928), -boilerplate (12:30:45.202) ~0.91, +boilerpate (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O19" authorId="0" shapeId="0">
       <text>
-        <t>+log* (12:53:22.757), -error (12:53:23.899), -Charlie (13:07:39.223), -. (13:19:44.184), -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168), -` (13:32:14.220), -Weekend (13:37:10.693), +am (00:00:00), +Charle (00:00:00), +, (00:00:00), +a (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +a (00:00:00), ++ (00:00:00), +b (00:00:00), +) (00:00:00), +; (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
+        <t>+log* (12:53:22.757), -error (12:53:23.899), -Charlie (13:07:39.223) ~0.86, -. (13:19:44.184) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -Weekend (13:37:10.693) ~0.00, +am (00:00:00), +Charle (00:00:00), +, (00:00:00), +a (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +a (00:00:00), ++ (00:00:00), +b (00:00:00), +) (00:00:00), +; (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
@@ -267,12 +267,12 @@
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
       <text>
-        <t>-: (12:29:02.589), -followed (12:31:10.973), +( (00:00:00), +folowed (00:00:00), +) (00:00:00)</t>
+        <t>-: (12:29:02.589), -followed (12:31:10.973) ~0.88, +( (00:00:00), +folowed (00:00:00), +) (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
       <text>
-        <t>-study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095), -Max (13:05:08.613), -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524), -" (13:05:23.089), -" (13:05:24.754), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -" (13:07:52.850), -" (13:07:53.974), -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437), -" (13:20:07.578), -" (13:20:08.157), -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +, (00:00:00), +myBoolean (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
+        <t>-study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095) ~0.00, -Max (13:05:08.613) ~0.67, -" (13:05:08.847) ~0.00, -" (13:05:18.869) ~0.00, -" (13:05:20.541) ~0.00, -eyes (13:05:22.524) ~0.75, -" (13:05:23.089) ~0.00, -" (13:05:24.754) ~0.00, -" (13:07:37.700) ~0.00, -Charlie (13:07:39.223) ~0.71, -" (13:07:39.689) ~0.00, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -" (13:10:58.977) ~0.00, -" (13:11:00.402) ~0.00, -" (13:11:05.379) ~0.00, -" (13:11:09.329) ~0.00, -" (13:11:10.342) ~0.00, -" (13:11:12.437) ~0.00, -" (13:20:07.578) ~0.00, -" (13:20:08.157) ~0.00, -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463) ~0.00, -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019) ~0.75, -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667) ~0.75, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.71, -Thursday (13:36:45.577) ~0.44, -Friday (13:36:53.097) ~0.50, -Weekend (13:37:10.693) ~0.86, -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +, (00:00:00), +myBoolean (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
@@ -292,12 +292,12 @@
     </comment>
     <comment ref="M24" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), +lesson (00:00:00), +) (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.83, +lesson (00:00:00), +) (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:42:36.696), -; (12:52:14.599), -furr (13:05:18.077), -" (13:07:52.850), -" (13:07:53.974), -+ (13:19:45.738), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:38.713), -, (13:29:49.778), -s3 (13:29:51.023), +fur (00:00:00), +' (00:00:00), +' (00:00:00), +* (00:00:00), +' (00:00:00), +' (00:00:00)</t>
+        <t>-; (12:42:36.696), -; (12:52:14.599), -furr (13:05:18.077) ~0.75, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -+ (13:19:45.738) ~0.00, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:38.713) ~0.00, -, (13:29:49.778), -s3 (13:29:51.023), +fur (00:00:00), +' (00:00:00), +' (00:00:00), +* (00:00:00), +' (00:00:00), +' (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E25" authorId="0" shapeId="0">
@@ -317,12 +317,12 @@
     </comment>
     <comment ref="M25" authorId="0" shapeId="0">
       <text>
-        <t>-JavaScript (12:24:24.306), -Lesson (12:24:25.593), -id (12:27:55.052), -My (12:28:56.380), -Emmet (12:28:58.636), -HTML (12:30:43.236), -Tab (12:31:12.499), -Enter (12:31:14.293), +javascript (00:00:00), +lesson (00:00:00), +Id (00:00:00), +my (00:00:00), +emmet (00:00:00), +html (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+        <t>-JavaScript (12:24:24.306) ~0.80, -Lesson (12:24:25.593) ~0.83, -id (12:27:55.052) ~0.50, -My (12:28:56.380) ~0.50, -Emmet (12:28:58.636) ~0.80, -HTML (12:30:43.236) ~0.00, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +javascript (00:00:00), +lesson (00:00:00), +Id (00:00:00), +my (00:00:00), +emmet (00:00:00), +html (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -at (12:35:31.858), -Karelia (12:35:33.317), -Karelia (12:46:59.354), -2 (12:48:52.350), -dog (13:05:03.658), -Max (13:05:08.613), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -Charlie (13:07:39.223), -dog (13:07:52.399), -Rex (13:11:00.170), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -I (13:30:59.741), -` (13:31:57.168), -I (13:32:08.777), -` (13:32:14.220), -August (13:33:55.549), -console (13:34:01.942), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -at (12:35:31.858) ~0.00, -Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -2 (12:48:52.350) ~0.00, -dog (13:05:03.658) ~0.67, -Max (13:05:08.613) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -dog (13:07:52.399) ~0.67, -Rex (13:11:00.170) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -I (13:30:59.741) ~0.00, -` (13:31:57.168) ~0.00, -I (13:32:08.777) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -console (13:34:01.942) ~0.86, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.67, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.71, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -342,12 +342,12 @@
     </comment>
     <comment ref="M30" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), -boilerplate (12:30:45.202), +lesson (00:00:00), +boilerdplate (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.83, -boilerplate (12:30:45.202) ~0.92, +lesson (00:00:00), +boilerdplate (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O30" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:47:19.402), -` (13:31:57.168), -` (13:32:14.220), +' (00:00:00), +' (00:00:00)</t>
+        <t>-; (12:47:19.402), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, +' (00:00:00), +' (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
@@ -367,12 +367,12 @@
     </comment>
     <comment ref="M31" authorId="0" shapeId="0">
       <text>
-        <t>-ordered (12:31:02.226), -Tab (12:31:12.499), -" (13:09:20.914), -" (13:09:20.924), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +orddr (00:00:00), +tab (00:00:00)</t>
+        <t>-ordered (12:31:02.226) ~0.57, -Tab (12:31:12.499) ~0.67, -" (13:09:20.914), -" (13:09:20.924), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +orddr (00:00:00), +tab (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O31" authorId="0" shapeId="0">
       <text>
-        <t>-; (13:02:35.373), -; (13:20:09.716), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -= (13:26:10.651), -; (13:26:12.162), -; (13:26:24.323), -! (13:28:16.362), -! (13:28:30.583), -36 (13:30:50.077), -; (13:32:15.376), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +35 (00:00:00), +; (00:00:00)</t>
+        <t>-; (13:02:35.373), -; (13:20:09.716), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -= (13:26:10.651), -; (13:26:12.162), -; (13:26:24.323), -! (13:28:16.362), -! (13:28:30.583), -36 (13:30:50.077) ~0.50, -; (13:32:15.376), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +35 (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
@@ -392,12 +392,12 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-! (12:24:11.928), -UTF (12:24:12.488), -= (12:24:13.188), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -/ (12:29:39.313), -Tab (12:31:12.499), -https (13:09:28.845), +utf (00:00:00), +- (00:00:00), +Javascript (00:00:00), +lesson (00:00:00), +tab (00:00:00), +html (00:00:00)</t>
+        <t>-! (12:24:11.928), -UTF (12:24:12.488) ~0.00, -= (12:24:13.188) ~0.00, -JavaScript (12:24:24.306) ~0.90, -Lesson (12:24:25.593) ~0.83, -/ (12:29:39.313), -Tab (12:31:12.499) ~0.67, -https (13:09:28.845) ~0.40, +utf (00:00:00), +- (00:00:00), +Javascript (00:00:00), +lesson (00:00:00), +tab (00:00:00), +html (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:35:33.317), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -. (13:07:09.027), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:17.407), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -36 (13:30:50.077), -; (13:31:07.806), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -August (13:33:55.549), -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -Weekend (13:37:10.693), -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +  (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +/ (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:35:33.317) ~0.86, -undefined (12:43:17.799) ~0.75, -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -. (13:07:09.027) ~0.00, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.91, -; (13:20:17.407), -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -August (13:33:55.549) ~0.83, -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.62, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967) ~0.88, -Weekend (13:37:10.693) ~0.71, -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +  (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +/ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E41" authorId="0" shapeId="0">
@@ -417,12 +417,12 @@
     </comment>
     <comment ref="M41" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +javaScript (00:00:00), +lesson (00:00:00), +ENter (00:00:00), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +&gt; (00:00:00), +mynumber (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +myArray (00:00:00), +) (00:00:00), +; (00:00:00), +' (00:00:00), +' (00:00:00), +Black (00:00:00), +Brown (00:00:00), +Kaali (00:00:00), +, (00:00:00), +Black (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +; (00:00:00), +a (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +a (00:00:00), +) (00:00:00), ++ (00:00:00), +5 (00:00:00), +; (00:00:00)</t>
+        <t>-&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306) ~0.90, -Lesson (12:24:25.593) ~0.83, -&lt; (12:27:55.192), -/ (12:27:55.202) ~0.00, -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293) ~0.80, -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +javaScript (00:00:00), +lesson (00:00:00), +ENter (00:00:00), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +&gt; (00:00:00), +mynumber (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +myArray (00:00:00), +) (00:00:00), +; (00:00:00), +' (00:00:00), +' (00:00:00), +Black (00:00:00), +Brown (00:00:00), +Kaali (00:00:00), +, (00:00:00), +Black (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +; (00:00:00), +a (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +a (00:00:00), +) (00:00:00), ++ (00:00:00), +5 (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O41" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095), -" (13:05:08.847), -black (13:05:20.120), -brown (13:05:24.043), -; (13:07:10.952), -Charlie (13:07:39.223), -black (13:11:11.856), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095) ~0.00, -" (13:05:08.847) ~0.00, -black (13:05:20.120) ~0.80, -brown (13:05:24.043) ~0.80, -; (13:07:10.952), -Charlie (13:07:39.223) ~0.43, -black (13:11:11.856) ~0.80, -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
@@ -437,17 +437,17 @@
     </comment>
     <comment ref="J42" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
+        <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
       </text>
     </comment>
     <comment ref="M42" authorId="0" shapeId="0">
       <text>
-        <t>-first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), +First (00:00:00), +Emnet (00:00:00), +abbbriviations (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
+        <t>-first (12:28:57.481) ~0.80, -Emmet (12:28:58.636) ~0.80, -abbreviations (12:29:01.416) ~0.86, -ol (12:29:38.973) ~0.50, -/ (12:29:39.313), -ol (12:29:39.333) ~0.50, -ol (12:30:53.144) ~0.50, +First (00:00:00), +Emnet (00:00:00), +abbbriviations (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520), +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
+        <t>-Karelia (12:35:33.317) ~0.86, -; (12:35:38.458), -Karelia (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520) ~0.67, +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
@@ -467,12 +467,12 @@
     </comment>
     <comment ref="M45" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), -abbreviations (12:29:01.416), -ordered (12:31:02.226), -list (12:31:03.447), +viewpoint (00:00:00), +abbreviation (00:00:00), +orderlist (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.78, -abbreviations (12:29:01.416) ~0.92, -ordered (12:31:02.226), -list (12:31:03.447), +viewpoint (00:00:00), +abbreviation (00:00:00), +orderlist (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O45" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:46:59.354), -Max (13:05:08.613), -Charlie (13:07:39.223), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -getDay (13:34:50.180), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -Charlie (13:07:39.223) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -getDay (13:34:50.180) ~0.71, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.83, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E46" authorId="0" shapeId="0">
@@ -492,12 +492,12 @@
     </comment>
     <comment ref="M46" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), -HTML (12:30:43.236), +Lession (00:00:00), +Html (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.86, -HTML (12:30:43.236) ~0.25, +Lession (00:00:00), +Html (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O46" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818), -default (13:37:00.967), +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
+        <t>-Karelia (12:46:59.354) ~0.88, +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077) ~0.75, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818) ~0.80, -default (13:37:00.967) ~0.86, +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E48" authorId="0" shapeId="0">
@@ -517,12 +517,12 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), -initial (12:24:13.118), -Lesson (12:24:25.593), -/ (12:29:39.313), -ordered (12:31:02.226), +Viewport (00:00:00), +intial (00:00:00), +lesson (00:00:00), +order (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.88, -initial (12:24:13.118) ~0.86, -Lesson (12:24:25.593) ~0.83, -/ (12:29:39.313), -ordered (12:31:02.226) ~0.71, +Viewport (00:00:00), +intial (00:00:00), +lesson (00:00:00), +order (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
       <text>
-        <t>-Charlie (13:07:39.223), -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678), +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
+        <t>-Charlie (13:07:39.223) ~0.86, -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066) ~0.86, -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -542,12 +542,12 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), -Enter (12:31:14.293), +viewpoint (00:00:00), +enter (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.78, -Enter (12:31:14.293) ~0.80, +viewpoint (00:00:00), +enter (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O50" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:35:38.458), -; (12:41:10.990), +log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053), -default (13:37:00.967), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
+        <t>-; (12:35:38.458), -; (12:41:10.990), +log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053) ~0.00, -default (13:37:00.967) ~0.14, +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
@@ -567,12 +567,12 @@
     </comment>
     <comment ref="M51" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), -abbreviations (12:29:01.416), +Lession (00:00:00), +abbreviatios (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.86, -abbreviations (12:29:01.416) ~0.92, +Lession (00:00:00), +abbreviatios (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O51" authorId="0" shapeId="0">
       <text>
-        <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030), -36 (13:30:50.077), +Karela (00:00:00), +22 (00:00:00)</t>
+        <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030) ~0.86, -36 (13:30:50.077) ~0.00, +Karela (00:00:00), +22 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E56" authorId="0" shapeId="0">
@@ -592,12 +592,12 @@
     </comment>
     <comment ref="M56" authorId="0" shapeId="0">
       <text>
-        <t>-container (12:30:48.969), -items (12:31:06.206), +containter (00:00:00), +item (00:00:00)</t>
+        <t>-container (12:30:48.969) ~0.90, -items (12:31:06.206) ~0.80, +containter (00:00:00), +item (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O56" authorId="0" shapeId="0">
       <text>
-        <t>-25 (12:33:49.617), -2 (12:33:50.650), -; (12:36:56.445), -Karelia (12:46:59.354), -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170), -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030), -! (13:28:16.362), -Karelia (13:28:30.418), -! (13:28:30.583), -" (13:29:31.463), -Karelia (13:29:38.066), -36 (13:30:50.077), -years (13:32:12.609), -; (13:32:15.376), -August (13:33:55.549), -24 (13:33:56.247), -2025 (13:33:58.460), +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
+        <t>-25 (12:33:49.617) ~0.00, -2 (12:33:50.650) ~0.00, -; (12:36:56.445), -Karelia (12:46:59.354) ~0.00, -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170) ~0.67, -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -" (13:29:31.463) ~0.00, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:32:12.609) ~0.80, -; (13:32:15.376), -August (13:33:55.549) ~0.00, -24 (13:33:56.247) ~0.50, -2025 (13:33:58.460) ~0.50, +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E59" authorId="0" shapeId="0">
@@ -617,12 +617,12 @@
     </comment>
     <comment ref="M59" authorId="0" shapeId="0">
       <text>
-        <t>-abbreviations (12:29:01.416), +abbreviation (00:00:00)</t>
+        <t>-abbreviations (12:29:01.416) ~0.92, +abbreviation (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:46:59.354), -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097), +karelia (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
+        <t>-Karelia (12:46:59.354) ~0.86, -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +karelia (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D61" authorId="0" shapeId="0">
@@ -647,17 +647,17 @@
     </comment>
     <comment ref="M61" authorId="0" shapeId="0">
       <text>
-        <t>-JavaScript (12:24:24.306), -Lesson (12:24:25.593), -first (12:28:57.481), -! (12:30:40.873), -ordered (12:31:02.226), -Tab (12:31:12.499), +java (00:00:00), +script (00:00:00), +lesson (00:00:00), +First (00:00:00), +Ordered (00:00:00), +tab (00:00:00)</t>
+        <t>-JavaScript (12:24:24.306), -Lesson (12:24:25.593) ~0.83, -first (12:28:57.481) ~0.80, -! (12:30:40.873), -ordered (12:31:02.226) ~0.86, -Tab (12:31:12.499) ~0.67, +java (00:00:00), +script (00:00:00), +lesson (00:00:00), +First (00:00:00), +Ordered (00:00:00), +tab (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O61" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -console (12:33:56.141), -myNumber (12:33:59.949), -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317), -! (12:42:04.755), -42 (12:42:11.528), -console (12:43:10.202), -Karelia (12:46:59.354), -Max (13:05:08.613), -appendChild (13:13:30.342), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -Karelia (13:29:38.066), -years (13:32:12.609), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00), +; (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -console (12:33:56.141) ~0.71, -myNumber (12:33:59.949) ~0.88, -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317) ~0.86, -! (12:42:04.755), -42 (12:42:11.528) ~0.67, -console (12:43:10.202) ~0.86, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -appendChild (13:13:30.342) ~0.91, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -Karelia (13:29:38.066) ~0.86, -years (13:32:12.609) ~0.80, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
@@ -677,12 +677,12 @@
     </comment>
     <comment ref="M62" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), -boilerplate (12:30:45.202), -Tab (12:31:12.499), -Enter (12:31:14.293), +Lession (00:00:00), +bolierplate (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.86, -boilerplate (12:30:45.202) ~0.82, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +Lession (00:00:00), +bolierplate (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O62" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:35:38.458), -brown (13:05:24.043), -; (13:12:34.331), -; (13:28:31.528), -36 (13:30:50.077), -; (13:34:00.044), +brows (00:00:00), +48 (00:00:00)</t>
+        <t>-; (12:35:38.458), -brown (13:05:24.043) ~0.80, -; (13:12:34.331), -; (13:28:31.528), -36 (13:30:50.077) ~0.00, -; (13:34:00.044), +brows (00:00:00), +48 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E66" authorId="0" shapeId="0">
@@ -702,17 +702,17 @@
     </comment>
     <comment ref="M66" authorId="0" shapeId="0">
       <text>
-        <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -HTML (12:30:43.236), -ordered (12:31:02.226), +Html (00:00:00), +order (00:00:00)</t>
+        <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -HTML (12:30:43.236) ~0.25, -ordered (12:31:02.226) ~0.71, +Html (00:00:00), +order (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O66" authorId="0" shapeId="0">
       <text>
-        <t>-oppositeBoolean (12:41:07.806), -oppositeBoolean (12:41:21.351), +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029), -log (13:19:44.775), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
+        <t>-oppositeBoolean (12:41:07.806) ~0.93, -oppositeBoolean (12:41:21.351) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029) ~0.00, -log (13:19:44.775) ~0.00, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
       <text>
-        <t>" (x3), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, karelia, max, muBoolean, my, orderd, t (x3), title, we, welcome (x3), Document*, log*</t>
+        <t>" (x2), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, karelia, max, muBoolean, my, orderd, t (x2), title, we, welcome (x2), Document*, log*</t>
       </text>
     </comment>
     <comment ref="H68" authorId="0" shapeId="0">
@@ -722,17 +722,17 @@
     </comment>
     <comment ref="J68" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +karelia (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
+        <t>+" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +karelia (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
       </text>
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
       <text>
-        <t>-  (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +" (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +my (00:00:00), +abbrevetion (00:00:00), +html (00:00:00), +orderd (00:00:00), +# (00:00:00), +itemes (00:00:00), +&gt; (00:00:00)</t>
+        <t>-  (00:00:00) ~0.00, +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380) ~0.50, -abbreviations (12:29:01.416) ~0.77, -HTML (12:30:43.236) ~0.00, -ordered (12:31:02.226) ~0.86, -3 (12:31:04.810) ~0.00, -items (12:31:06.206) ~0.83, -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -radufromfinland (13:09:39.343) ~0.93, -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +my (00:00:00), +abbrevetion (00:00:00), +html (00:00:00), +orderd (00:00:00), +# (00:00:00), +itemes (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736), +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
+        <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Karelia (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:15.871), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970) ~0.00, -Wednesday (13:36:38.686) ~0.11, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +i (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
@@ -752,12 +752,12 @@
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), -! (12:30:40.873), +" (00:00:00), +lesson (00:00:00), +/ (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.83, -! (12:30:40.873), +" (00:00:00), +lesson (00:00:00), +/ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myBoolean (12:36:27.967), -Karelia (12:46:59.354), -. (12:58:07.899), -; (13:02:35.373), -Max (13:05:08.613), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -age (13:30:48.674), -36 (13:30:50.077), -` (13:32:14.220), -; (13:32:15.376), -console (13:34:46.231), -} (13:35:58.376), -Weekend (13:37:10.693), -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -Karelia (12:46:59.354) ~0.86, -. (12:58:07.899) ~0.00, -; (13:02:35.373) ~0.00, -Max (13:05:08.613) ~0.33, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010), -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -36 (13:30:50.077) ~0.00, -` (13:32:14.220) ~0.00, -; (13:32:15.376), -console (13:34:46.231) ~0.86, -} (13:35:58.376), -Weekend (13:37:10.693) ~0.71, -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H71" authorId="0" shapeId="0">
@@ -792,12 +792,12 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), +viewpoint (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.78, +viewpoint (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
       <text>
-        <t>-study (12:35:31.258), -Karelia (12:35:33.317), -36 (13:30:50.077), -years (13:31:05.818), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
+        <t>-study (12:35:31.258) ~0.80, -Karelia (12:35:33.317) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:31:05.818) ~0.80, -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E73" authorId="0" shapeId="0">
@@ -822,7 +822,7 @@
     </comment>
     <comment ref="O73" authorId="0" shapeId="0">
       <text>
-        <t>-36 (13:30:50.077), +21 (00:00:00)</t>
+        <t>-36 (13:30:50.077) ~0.00, +21 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E75" authorId="0" shapeId="0">
@@ -837,17 +837,17 @@
     </comment>
     <comment ref="J75" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +HTMl (00:00:00), +browen (00:00:00), +charlie (00:00:00), +friday (00:00:00), +getday (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +saturday (00:00:00), +tab (00:00:00), +thursday (00:00:00), +today (00:00:00), +tuesday (00:00:00), +underfined (00:00:00), +view (00:00:00), +yeasrs (00:00:00), -viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), -myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -" (13:29:13.699), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
+        <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +HTMl (00:00:00), +browen (00:00:00), +charlie (00:00:00), +friday (00:00:00), +getday (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +saturday (00:00:00), +tab (00:00:00), +thursday (00:00:00), +today (00:00:00), +tuesday (00:00:00), +underfined (00:00:00), +view (00:00:00), +yeasrs (00:00:00), -viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), -myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
       </text>
     </comment>
     <comment ref="M75" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), +view (00:00:00), +port (00:00:00), +HTMl (00:00:00), +tab (00:00:00)</t>
+        <t>-viewport (12:24:12.738), -HTML (12:30:43.236) ~0.75, -Tab (12:31:12.499) ~0.67, +view (00:00:00), +port (00:00:00), +HTMl (00:00:00), +tab (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O75" authorId="0" shapeId="0">
       <text>
-        <t>-myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -" (13:29:13.699), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +today (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
+        <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108), -myBoolean (12:41:00.416) ~0.89, -; (12:41:04.494), -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, -Karelia (12:46:59.354) ~0.86, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613) ~0.67, -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -; (13:26:07.158), -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759) ~0.00, -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -years (13:32:12.609) ~0.83, -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019) ~0.25, -getDay (13:35:54.315) ~0.83, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.44, -Thursday (13:36:45.577) ~0.50, -Friday (13:36:53.097) ~0.38, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +today (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -862,12 +862,12 @@
     </comment>
     <comment ref="M78" authorId="0" shapeId="0">
       <text>
-        <t>-html (12:24:12.048), -JavaScript (12:24:24.306), -followed (12:31:10.973), +HTML (00:00:00), +" (00:00:00), +" (00:00:00), +Javascript (00:00:00), +allowed (00:00:00), +  (00:00:00)</t>
+        <t>-html (12:24:12.048) ~0.00, -JavaScript (12:24:24.306) ~0.90, -followed (12:31:10.973) ~0.75, +HTML (00:00:00), +" (00:00:00), +" (00:00:00), +Javascript (00:00:00), +allowed (00:00:00), +  (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O78" authorId="0" shapeId="0">
       <text>
-        <t>-log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -36 (13:30:50.077), -Monday (13:36:18.214), -; (13:38:17.969), +lig (00:00:00), +oppositeBolean (00:00:00), +26 (00:00:00), +Mondayy (00:00:00), +, (00:00:00)</t>
+        <t>-log (12:35:41.570) ~0.67, -oppositeBoolean (12:36:43.817) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -36 (13:30:50.077) ~0.50, -Monday (13:36:18.214) ~0.86, -; (13:38:17.969) ~0.00, +lig (00:00:00), +oppositeBolean (00:00:00), +26 (00:00:00), +Mondayy (00:00:00), +, (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E79" authorId="0" shapeId="0">
@@ -887,12 +887,12 @@
     </comment>
     <comment ref="M79" authorId="0" shapeId="0">
       <text>
-        <t>-ol (12:30:53.144), -all (12:31:09.440), +old (00:00:00), +All (00:00:00)</t>
+        <t>-ol (12:30:53.144) ~0.67, -all (12:31:09.440) ~0.67, +old (00:00:00), +All (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O79" authorId="0" shapeId="0">
       <text>
-        <t>-; (13:05:06.814), -% (13:22:03.842), -36 (13:30:50.077), +&amp; (00:00:00), +! (00:00:00), +31 (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +someDate (00:00:00), +. (00:00:00), +getDay (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+        <t>-; (13:05:06.814), -% (13:22:03.842) ~0.00, -36 (13:30:50.077) ~0.50, +&amp; (00:00:00), +! (00:00:00), +31 (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +someDate (00:00:00), +. (00:00:00), +getDay (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E81" authorId="0" shapeId="0">
@@ -912,12 +912,12 @@
     </comment>
     <comment ref="M81" authorId="0" shapeId="0">
       <text>
-        <t>-Tab (12:31:12.499), -Enter (12:31:14.293), +list (00:00:00), +TAB (00:00:00), +enter (00:00:00)</t>
+        <t>-Tab (12:31:12.499) ~0.33, -Enter (12:31:14.293) ~0.80, +list (00:00:00), +TAB (00:00:00), +enter (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O81" authorId="0" shapeId="0">
       <text>
-        <t>-ABC (12:42:20.731), -; (13:02:35.373), -Welcome (13:28:13.560), -Welcome (13:28:27.998), -Welcome (13:29:34.675), -36 (13:30:50.077), +abc (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +20 (00:00:00)</t>
+        <t>-ABC (12:42:20.731) ~0.00, -; (13:02:35.373), -Welcome (13:28:13.560) ~0.86, -Welcome (13:28:27.998) ~0.86, -Welcome (13:29:34.675) ~0.86, -36 (13:30:50.077) ~0.00, +abc (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +20 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E82" authorId="0" shapeId="0">
@@ -937,7 +937,7 @@
     </comment>
     <comment ref="O82" authorId="0" shapeId="0">
       <text>
-        <t>-ABC (12:42:20.731), -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354), -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077), -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077), -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
+        <t>-ABC (12:42:20.731) ~0.00, -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354) ~0.00, -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077) ~0.75, -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E83" authorId="0" shapeId="0">
@@ -957,12 +957,12 @@
     </comment>
     <comment ref="M83" authorId="0" shapeId="0">
       <text>
-        <t>-: (12:29:02.589), -ordered (12:31:02.226), -Tab (12:31:12.499), -Enter (12:31:14.293), +; (00:00:00), +orderd (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+        <t>-: (12:29:02.589) ~0.00, -ordered (12:31:02.226) ~0.86, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +; (00:00:00), +orderd (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O83" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:47:24.675), +log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667), -Thursday (13:36:45.577), +somedate (00:00:00), +Thrusday (00:00:00)</t>
+        <t>-; (12:47:24.675), +log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667) ~0.88, -Thursday (13:36:45.577) ~0.75, +somedate (00:00:00), +Thrusday (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-Tab (12:31:12.499), +tab (00:00:00)</t>
+          <t>-Tab (12:31:12.499) ~0.67, +tab (00:00:00)</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-Karelia (12:35:33.317), -Karelia (12:46:59.354), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066), -36 (13:30:50.077), -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881), -` (13:31:57.168), -` (13:32:14.220), -; (13:33:31.713), -August (13:33:55.549), -Wednesday (13:36:38.686), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736), +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
+          <t>-Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.90, -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881) ~0.75, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -; (13:33:31.713), -August (13:33:55.549) ~0.83, -Wednesday (13:36:38.686) ~0.89, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736) ~0.83, +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-JavaScript (12:24:24.306), +Javascript (00:00:00)</t>
+          <t>-JavaScript (12:24:24.306) ~0.90, +Javascript (00:00:00)</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -Karelia (12:46:59.354), -Karelia (13:28:16.030), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
+          <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -Karelia (12:46:59.354) ~0.86, -Karelia (13:28:16.030) ~0.86, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-abbreviations (12:29:01.416), +abbreaviations (00:00:00)</t>
+          <t>-abbreviations (12:29:01.416) ~0.93, +abbreaviations (00:00:00)</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-Karelia (12:35:33.317), -Max (13:05:08.613), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560), -Date (13:33:53.451), -August (13:33:55.549), +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
+          <t>-Karelia (12:35:33.317) ~0.86, -Max (13:05:08.613) ~0.67, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560) ~0.86, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-! (12:24:11.928), -boilerplate (12:30:45.202), +boilerpate (00:00:00)</t>
+          <t>-! (12:24:11.928), -boilerplate (12:30:45.202) ~0.91, +boilerpate (00:00:00)</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>+log* (12:53:22.757), -error (12:53:23.899), -Charlie (13:07:39.223), -. (13:19:44.184), -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168), -` (13:32:14.220), -Weekend (13:37:10.693), +am (00:00:00), +Charle (00:00:00), +, (00:00:00), +a (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +a (00:00:00), ++ (00:00:00), +b (00:00:00), +) (00:00:00), +; (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
+          <t>+log* (12:53:22.757), -error (12:53:23.899), -Charlie (13:07:39.223) ~0.86, -. (13:19:44.184) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -Weekend (13:37:10.693) ~0.00, +am (00:00:00), +Charle (00:00:00), +, (00:00:00), +a (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +a (00:00:00), ++ (00:00:00), +b (00:00:00), +) (00:00:00), +; (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2239,15 +2239,15 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-: (12:29:02.589), -followed (12:31:10.973), +( (00:00:00), +folowed (00:00:00), +) (00:00:00)</t>
+          <t>-: (12:29:02.589), -followed (12:31:10.973) ~0.88, +( (00:00:00), +folowed (00:00:00), +) (00:00:00)</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095), -Max (13:05:08.613), -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524), -" (13:05:23.089), -" (13:05:24.754), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -" (13:07:52.850), -" (13:07:53.974), -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437), -" (13:20:07.578), -" (13:20:08.157), -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +, (00:00:00), +myBoolean (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
+          <t>-study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095) ~0.00, -Max (13:05:08.613) ~0.67, -" (13:05:08.847) ~0.00, -" (13:05:18.869) ~0.00, -" (13:05:20.541) ~0.00, -eyes (13:05:22.524) ~0.75, -" (13:05:23.089) ~0.00, -" (13:05:24.754) ~0.00, -" (13:07:37.700) ~0.00, -Charlie (13:07:39.223) ~0.71, -" (13:07:39.689) ~0.00, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -" (13:10:58.977) ~0.00, -" (13:11:00.402) ~0.00, -" (13:11:05.379) ~0.00, -" (13:11:09.329) ~0.00, -" (13:11:10.342) ~0.00, -" (13:11:12.437) ~0.00, -" (13:20:07.578) ~0.00, -" (13:20:08.157) ~0.00, -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463) ~0.00, -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019) ~0.75, -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667) ~0.75, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.71, -Thursday (13:36:45.577) ~0.44, -Friday (13:36:53.097) ~0.50, -Weekend (13:37:10.693) ~0.86, -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +, (00:00:00), +myBoolean (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), +lesson (00:00:00), +) (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.83, +lesson (00:00:00), +) (00:00:00)</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-; (12:42:36.696), -; (12:52:14.599), -furr (13:05:18.077), -" (13:07:52.850), -" (13:07:53.974), -+ (13:19:45.738), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:38.713), -, (13:29:49.778), -s3 (13:29:51.023), +fur (00:00:00), +' (00:00:00), +' (00:00:00), +* (00:00:00), +' (00:00:00), +' (00:00:00)</t>
+          <t>-; (12:42:36.696), -; (12:52:14.599), -furr (13:05:18.077) ~0.75, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -+ (13:19:45.738) ~0.00, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:38.713) ~0.00, -, (13:29:49.778), -s3 (13:29:51.023), +fur (00:00:00), +' (00:00:00), +' (00:00:00), +* (00:00:00), +' (00:00:00), +' (00:00:00)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2455,15 +2455,15 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-JavaScript (12:24:24.306), -Lesson (12:24:25.593), -id (12:27:55.052), -My (12:28:56.380), -Emmet (12:28:58.636), -HTML (12:30:43.236), -Tab (12:31:12.499), -Enter (12:31:14.293), +javascript (00:00:00), +lesson (00:00:00), +Id (00:00:00), +my (00:00:00), +emmet (00:00:00), +html (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+          <t>-JavaScript (12:24:24.306) ~0.80, -Lesson (12:24:25.593) ~0.83, -id (12:27:55.052) ~0.50, -My (12:28:56.380) ~0.50, -Emmet (12:28:58.636) ~0.80, -HTML (12:30:43.236) ~0.00, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +javascript (00:00:00), +lesson (00:00:00), +Id (00:00:00), +my (00:00:00), +emmet (00:00:00), +html (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>93.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -at (12:35:31.858), -Karelia (12:35:33.317), -Karelia (12:46:59.354), -2 (12:48:52.350), -dog (13:05:03.658), -Max (13:05:08.613), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -Charlie (13:07:39.223), -dog (13:07:52.399), -Rex (13:11:00.170), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -I (13:30:59.741), -` (13:31:57.168), -I (13:32:08.777), -` (13:32:14.220), -August (13:33:55.549), -console (13:34:01.942), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -at (12:35:31.858) ~0.00, -Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -2 (12:48:52.350) ~0.00, -dog (13:05:03.658) ~0.67, -Max (13:05:08.613) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -dog (13:07:52.399) ~0.67, -Rex (13:11:00.170) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -I (13:30:59.741) ~0.00, -` (13:31:57.168) ~0.00, -I (13:32:08.777) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -console (13:34:01.942) ~0.86, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.67, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.71, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), -boilerplate (12:30:45.202), +lesson (00:00:00), +boilerdplate (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.83, -boilerplate (12:30:45.202) ~0.92, +lesson (00:00:00), +boilerdplate (00:00:00)</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-; (12:47:19.402), -` (13:31:57.168), -` (13:32:14.220), +' (00:00:00), +' (00:00:00)</t>
+          <t>-; (12:47:19.402), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, +' (00:00:00), +' (00:00:00)</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-ordered (12:31:02.226), -Tab (12:31:12.499), -" (13:09:20.914), -" (13:09:20.924), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +orddr (00:00:00), +tab (00:00:00)</t>
+          <t>-ordered (12:31:02.226) ~0.57, -Tab (12:31:12.499) ~0.67, -" (13:09:20.914), -" (13:09:20.924), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +orddr (00:00:00), +tab (00:00:00)</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-; (13:02:35.373), -; (13:20:09.716), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -= (13:26:10.651), -; (13:26:12.162), -; (13:26:24.323), -! (13:28:16.362), -! (13:28:30.583), -36 (13:30:50.077), -; (13:32:15.376), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +35 (00:00:00), +; (00:00:00)</t>
+          <t>-; (13:02:35.373), -; (13:20:09.716), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -= (13:26:10.651), -; (13:26:12.162), -; (13:26:24.323), -! (13:28:16.362), -! (13:28:30.583), -36 (13:30:50.077) ~0.50, -; (13:32:15.376), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +35 (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-! (12:24:11.928), -UTF (12:24:12.488), -= (12:24:13.188), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -/ (12:29:39.313), -Tab (12:31:12.499), -https (13:09:28.845), +utf (00:00:00), +- (00:00:00), +Javascript (00:00:00), +lesson (00:00:00), +tab (00:00:00), +html (00:00:00)</t>
+          <t>-! (12:24:11.928), -UTF (12:24:12.488) ~0.00, -= (12:24:13.188) ~0.00, -JavaScript (12:24:24.306) ~0.90, -Lesson (12:24:25.593) ~0.83, -/ (12:29:39.313), -Tab (12:31:12.499) ~0.67, -https (13:09:28.845) ~0.40, +utf (00:00:00), +- (00:00:00), +Javascript (00:00:00), +lesson (00:00:00), +tab (00:00:00), +html (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:35:33.317), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -. (13:07:09.027), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:17.407), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -36 (13:30:50.077), -; (13:31:07.806), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -August (13:33:55.549), -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -Weekend (13:37:10.693), -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +  (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +/ (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:35:33.317) ~0.86, -undefined (12:43:17.799) ~0.75, -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -. (13:07:09.027) ~0.00, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.91, -; (13:20:17.407), -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -August (13:33:55.549) ~0.83, -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.62, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967) ~0.88, -Weekend (13:37:10.693) ~0.71, -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +  (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +/ (00:00:00)</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>-&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +javaScript (00:00:00), +lesson (00:00:00), +ENter (00:00:00), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +&gt; (00:00:00), +mynumber (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +myArray (00:00:00), +) (00:00:00), +; (00:00:00), +' (00:00:00), +' (00:00:00), +Black (00:00:00), +Brown (00:00:00), +Kaali (00:00:00), +, (00:00:00), +Black (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +; (00:00:00), +a (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +a (00:00:00), +) (00:00:00), ++ (00:00:00), +5 (00:00:00), +; (00:00:00)</t>
+          <t>-&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306) ~0.90, -Lesson (12:24:25.593) ~0.83, -&lt; (12:27:55.192), -/ (12:27:55.202) ~0.00, -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293) ~0.80, -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +javaScript (00:00:00), +lesson (00:00:00), +ENter (00:00:00), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +&gt; (00:00:00), +mynumber (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +myArray (00:00:00), +) (00:00:00), +; (00:00:00), +' (00:00:00), +' (00:00:00), +Black (00:00:00), +Brown (00:00:00), +Kaali (00:00:00), +, (00:00:00), +Black (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +; (00:00:00), +a (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +a (00:00:00), +) (00:00:00), ++ (00:00:00), +5 (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095), -" (13:05:08.847), -black (13:05:20.120), -brown (13:05:24.043), -; (13:07:10.952), -Charlie (13:07:39.223), -black (13:11:11.856), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095) ~0.00, -" (13:05:08.847) ~0.00, -black (13:05:20.120) ~0.80, -brown (13:05:24.043) ~0.80, -; (13:07:10.952), -Charlie (13:07:39.223) ~0.43, -black (13:11:11.856) ~0.80, -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3222,11 +3222,11 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
+          <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3235,15 +3235,15 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), +First (00:00:00), +Emnet (00:00:00), +abbbriviations (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
+          <t>-first (12:28:57.481) ~0.80, -Emmet (12:28:58.636) ~0.80, -abbreviations (12:29:01.416) ~0.86, -ol (12:29:38.973) ~0.50, -/ (12:29:39.313), -ol (12:29:39.333) ~0.50, -ol (12:30:53.144) ~0.50, +First (00:00:00), +Emnet (00:00:00), +abbbriviations (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520), +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
+          <t>-Karelia (12:35:33.317) ~0.86, -; (12:35:38.458), -Karelia (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520) ~0.67, +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), -abbreviations (12:29:01.416), -ordered (12:31:02.226), -list (12:31:03.447), +viewpoint (00:00:00), +abbreviation (00:00:00), +orderlist (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.78, -abbreviations (12:29:01.416) ~0.92, -ordered (12:31:02.226), -list (12:31:03.447), +viewpoint (00:00:00), +abbreviation (00:00:00), +orderlist (00:00:00)</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:46:59.354), -Max (13:05:08.613), -Charlie (13:07:39.223), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -getDay (13:34:50.180), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -Charlie (13:07:39.223) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -getDay (13:34:50.180) ~0.71, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.83, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), -HTML (12:30:43.236), +Lession (00:00:00), +Html (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.86, -HTML (12:30:43.236) ~0.25, +Lession (00:00:00), +Html (00:00:00)</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818), -default (13:37:00.967), +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
+          <t>-Karelia (12:46:59.354) ~0.88, +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077) ~0.75, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818) ~0.80, -default (13:37:00.967) ~0.86, +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), -initial (12:24:13.118), -Lesson (12:24:25.593), -/ (12:29:39.313), -ordered (12:31:02.226), +Viewport (00:00:00), +intial (00:00:00), +lesson (00:00:00), +order (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.88, -initial (12:24:13.118) ~0.86, -Lesson (12:24:25.593) ~0.83, -/ (12:29:39.313), -ordered (12:31:02.226) ~0.71, +Viewport (00:00:00), +intial (00:00:00), +lesson (00:00:00), +order (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-Charlie (13:07:39.223), -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678), +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
+          <t>-Charlie (13:07:39.223) ~0.86, -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066) ~0.86, -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), -Enter (12:31:14.293), +viewpoint (00:00:00), +enter (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.78, -Enter (12:31:14.293) ~0.80, +viewpoint (00:00:00), +enter (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>-; (12:35:38.458), -; (12:41:10.990), +log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053), -default (13:37:00.967), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
+          <t>-; (12:35:38.458), -; (12:41:10.990), +log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053) ~0.00, -default (13:37:00.967) ~0.14, +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), -abbreviations (12:29:01.416), +Lession (00:00:00), +abbreviatios (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.86, -abbreviations (12:29:01.416) ~0.92, +Lession (00:00:00), +abbreviatios (00:00:00)</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030), -36 (13:30:50.077), +Karela (00:00:00), +22 (00:00:00)</t>
+          <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030) ~0.86, -36 (13:30:50.077) ~0.00, +Karela (00:00:00), +22 (00:00:00)</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>-container (12:30:48.969), -items (12:31:06.206), +containter (00:00:00), +item (00:00:00)</t>
+          <t>-container (12:30:48.969) ~0.90, -items (12:31:06.206) ~0.80, +containter (00:00:00), +item (00:00:00)</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>-25 (12:33:49.617), -2 (12:33:50.650), -; (12:36:56.445), -Karelia (12:46:59.354), -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170), -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030), -! (13:28:16.362), -Karelia (13:28:30.418), -! (13:28:30.583), -" (13:29:31.463), -Karelia (13:29:38.066), -36 (13:30:50.077), -years (13:32:12.609), -; (13:32:15.376), -August (13:33:55.549), -24 (13:33:56.247), -2025 (13:33:58.460), +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
+          <t>-25 (12:33:49.617) ~0.00, -2 (12:33:50.650) ~0.00, -; (12:36:56.445), -Karelia (12:46:59.354) ~0.00, -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170) ~0.67, -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -" (13:29:31.463) ~0.00, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:32:12.609) ~0.80, -; (13:32:15.376), -August (13:33:55.549) ~0.00, -24 (13:33:56.247) ~0.50, -2025 (13:33:58.460) ~0.50, +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>-abbreviations (12:29:01.416), +abbreviation (00:00:00)</t>
+          <t>-abbreviations (12:29:01.416) ~0.92, +abbreviation (00:00:00)</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-Karelia (12:46:59.354), -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097), +karelia (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
+          <t>-Karelia (12:46:59.354) ~0.86, -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +karelia (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>-JavaScript (12:24:24.306), -Lesson (12:24:25.593), -first (12:28:57.481), -! (12:30:40.873), -ordered (12:31:02.226), -Tab (12:31:12.499), +java (00:00:00), +script (00:00:00), +lesson (00:00:00), +First (00:00:00), +Ordered (00:00:00), +tab (00:00:00)</t>
+          <t>-JavaScript (12:24:24.306), -Lesson (12:24:25.593) ~0.83, -first (12:28:57.481) ~0.80, -! (12:30:40.873), -ordered (12:31:02.226) ~0.86, -Tab (12:31:12.499) ~0.67, +java (00:00:00), +script (00:00:00), +lesson (00:00:00), +First (00:00:00), +Ordered (00:00:00), +tab (00:00:00)</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -console (12:33:56.141), -myNumber (12:33:59.949), -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317), -! (12:42:04.755), -42 (12:42:11.528), -console (12:43:10.202), -Karelia (12:46:59.354), -Max (13:05:08.613), -appendChild (13:13:30.342), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -Karelia (13:29:38.066), -years (13:32:12.609), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00), +; (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -console (12:33:56.141) ~0.71, -myNumber (12:33:59.949) ~0.88, -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317) ~0.86, -! (12:42:04.755), -42 (12:42:11.528) ~0.67, -console (12:43:10.202) ~0.86, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -appendChild (13:13:30.342) ~0.91, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -Karelia (13:29:38.066) ~0.86, -years (13:32:12.609) ~0.80, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), -boilerplate (12:30:45.202), -Tab (12:31:12.499), -Enter (12:31:14.293), +Lession (00:00:00), +bolierplate (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.86, -boilerplate (12:30:45.202) ~0.82, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +Lession (00:00:00), +bolierplate (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
         </is>
       </c>
       <c r="O62" t="n">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>-; (12:35:38.458), -brown (13:05:24.043), -; (13:12:34.331), -; (13:28:31.528), -36 (13:30:50.077), -; (13:34:00.044), +brows (00:00:00), +48 (00:00:00)</t>
+          <t>-; (12:35:38.458), -brown (13:05:24.043) ~0.80, -; (13:12:34.331), -; (13:28:31.528), -36 (13:30:50.077) ~0.00, -; (13:34:00.044), +brows (00:00:00), +48 (00:00:00)</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -HTML (12:30:43.236), -ordered (12:31:02.226), +Html (00:00:00), +order (00:00:00)</t>
+          <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -HTML (12:30:43.236) ~0.25, -ordered (12:31:02.226) ~0.71, +Html (00:00:00), +order (00:00:00)</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>-oppositeBoolean (12:41:07.806), -oppositeBoolean (12:41:21.351), +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029), -log (13:19:44.775), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
+          <t>-oppositeBoolean (12:41:07.806) ~0.93, -oppositeBoolean (12:41:21.351) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029) ~0.00, -log (13:19:44.775) ~0.00, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -4511,11 +4511,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>" (x3), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, karelia, max, muBoolean, my, orderd, t (x3), title, we, welcome (x3), Document*, log*</t>
+          <t>" (x2), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, karelia, max, muBoolean, my, orderd, t (x2), title, we, welcome (x2), Document*, log*</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4530,28 +4530,28 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>89.2</v>
+        <v>89.7</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +karelia (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
+          <t>+" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +karelia (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
-        <v>87</v>
+        <v>87.5</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>-  (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +" (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +my (00:00:00), +abbrevetion (00:00:00), +html (00:00:00), +orderd (00:00:00), +# (00:00:00), +itemes (00:00:00), +&gt; (00:00:00)</t>
+          <t>-  (00:00:00) ~0.00, +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380) ~0.50, -abbreviations (12:29:01.416) ~0.77, -HTML (12:30:43.236) ~0.00, -ordered (12:31:02.226) ~0.86, -3 (12:31:04.810) ~0.00, -items (12:31:06.206) ~0.83, -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -radufromfinland (13:09:39.343) ~0.93, -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +my (00:00:00), +abbrevetion (00:00:00), +html (00:00:00), +orderd (00:00:00), +# (00:00:00), +itemes (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>89.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736), +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
+          <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Karelia (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:15.871), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970) ~0.00, -Wednesday (13:36:38.686) ~0.11, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +i (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), -! (12:30:40.873), +" (00:00:00), +lesson (00:00:00), +/ (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.83, -! (12:30:40.873), +" (00:00:00), +lesson (00:00:00), +/ (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myBoolean (12:36:27.967), -Karelia (12:46:59.354), -. (12:58:07.899), -; (13:02:35.373), -Max (13:05:08.613), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -age (13:30:48.674), -36 (13:30:50.077), -` (13:32:14.220), -; (13:32:15.376), -console (13:34:46.231), -} (13:35:58.376), -Weekend (13:37:10.693), -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -Karelia (12:46:59.354) ~0.86, -. (12:58:07.899) ~0.00, -; (13:02:35.373) ~0.00, -Max (13:05:08.613) ~0.33, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010), -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -36 (13:30:50.077) ~0.00, -` (13:32:14.220) ~0.00, -; (13:32:15.376), -console (13:34:46.231) ~0.86, -} (13:35:58.376), -Weekend (13:37:10.693) ~0.71, -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), +viewpoint (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.78, +viewpoint (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-study (12:35:31.258), -Karelia (12:35:33.317), -36 (13:30:50.077), -years (13:31:05.818), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
+          <t>-study (12:35:31.258) ~0.80, -Karelia (12:35:33.317) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:31:05.818) ~0.80, -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>-36 (13:30:50.077), +21 (00:00:00)</t>
+          <t>-36 (13:30:50.077) ~0.00, +21 (00:00:00)</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -4944,11 +4944,11 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +HTMl (00:00:00), +browen (00:00:00), +charlie (00:00:00), +friday (00:00:00), +getday (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +saturday (00:00:00), +tab (00:00:00), +thursday (00:00:00), +today (00:00:00), +tuesday (00:00:00), +underfined (00:00:00), +view (00:00:00), +yeasrs (00:00:00), -viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), -myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -" (13:29:13.699), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
+          <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +HTMl (00:00:00), +browen (00:00:00), +charlie (00:00:00), +friday (00:00:00), +getday (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +saturday (00:00:00), +tab (00:00:00), +thursday (00:00:00), +today (00:00:00), +tuesday (00:00:00), +underfined (00:00:00), +view (00:00:00), +yeasrs (00:00:00), -viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), -myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4957,15 +4957,15 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), +view (00:00:00), +port (00:00:00), +HTMl (00:00:00), +tab (00:00:00)</t>
+          <t>-viewport (12:24:12.738), -HTML (12:30:43.236) ~0.75, -Tab (12:31:12.499) ~0.67, +view (00:00:00), +port (00:00:00), +HTMl (00:00:00), +tab (00:00:00)</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>-myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -" (13:29:13.699), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +today (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
+          <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108), -myBoolean (12:41:00.416) ~0.89, -; (12:41:04.494), -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, -Karelia (12:46:59.354) ~0.86, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613) ~0.67, -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -; (13:26:07.158), -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759) ~0.00, -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -years (13:32:12.609) ~0.83, -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019) ~0.25, -getDay (13:35:54.315) ~0.83, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.44, -Thursday (13:36:45.577) ~0.50, -Friday (13:36:53.097) ~0.38, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +today (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>-html (12:24:12.048), -JavaScript (12:24:24.306), -followed (12:31:10.973), +HTML (00:00:00), +" (00:00:00), +" (00:00:00), +Javascript (00:00:00), +allowed (00:00:00), +  (00:00:00)</t>
+          <t>-html (12:24:12.048) ~0.00, -JavaScript (12:24:24.306) ~0.90, -followed (12:31:10.973) ~0.75, +HTML (00:00:00), +" (00:00:00), +" (00:00:00), +Javascript (00:00:00), +allowed (00:00:00), +  (00:00:00)</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>-log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -36 (13:30:50.077), -Monday (13:36:18.214), -; (13:38:17.969), +lig (00:00:00), +oppositeBolean (00:00:00), +26 (00:00:00), +Mondayy (00:00:00), +, (00:00:00)</t>
+          <t>-log (12:35:41.570) ~0.67, -oppositeBoolean (12:36:43.817) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -36 (13:30:50.077) ~0.50, -Monday (13:36:18.214) ~0.86, -; (13:38:17.969) ~0.00, +lig (00:00:00), +oppositeBolean (00:00:00), +26 (00:00:00), +Mondayy (00:00:00), +, (00:00:00)</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>-ol (12:30:53.144), -all (12:31:09.440), +old (00:00:00), +All (00:00:00)</t>
+          <t>-ol (12:30:53.144) ~0.67, -all (12:31:09.440) ~0.67, +old (00:00:00), +All (00:00:00)</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>-; (13:05:06.814), -% (13:22:03.842), -36 (13:30:50.077), +&amp; (00:00:00), +! (00:00:00), +31 (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +someDate (00:00:00), +. (00:00:00), +getDay (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+          <t>-; (13:05:06.814), -% (13:22:03.842) ~0.00, -36 (13:30:50.077) ~0.50, +&amp; (00:00:00), +! (00:00:00), +31 (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +someDate (00:00:00), +. (00:00:00), +getDay (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>-Tab (12:31:12.499), -Enter (12:31:14.293), +list (00:00:00), +TAB (00:00:00), +enter (00:00:00)</t>
+          <t>-Tab (12:31:12.499) ~0.33, -Enter (12:31:14.293) ~0.80, +list (00:00:00), +TAB (00:00:00), +enter (00:00:00)</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>-ABC (12:42:20.731), -; (13:02:35.373), -Welcome (13:28:13.560), -Welcome (13:28:27.998), -Welcome (13:29:34.675), -36 (13:30:50.077), +abc (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +20 (00:00:00)</t>
+          <t>-ABC (12:42:20.731) ~0.00, -; (13:02:35.373), -Welcome (13:28:13.560) ~0.86, -Welcome (13:28:27.998) ~0.86, -Welcome (13:29:34.675) ~0.86, -36 (13:30:50.077) ~0.00, +abc (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +20 (00:00:00)</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>-ABC (12:42:20.731), -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354), -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077), -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077), -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
+          <t>-ABC (12:42:20.731) ~0.00, -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354) ~0.00, -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077) ~0.75, -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>-: (12:29:02.589), -ordered (12:31:02.226), -Tab (12:31:12.499), -Enter (12:31:14.293), +; (00:00:00), +orderd (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+          <t>-: (12:29:02.589) ~0.00, -ordered (12:31:02.226) ~0.86, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +; (00:00:00), +orderd (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>-; (12:47:24.675), +log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667), -Thursday (13:36:45.577), +somedate (00:00:00), +Thrusday (00:00:00)</t>
+          <t>-; (12:47:24.675), +log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667) ~0.88, -Thursday (13:36:45.577) ~0.75, +somedate (00:00:00), +Thrusday (00:00:00)</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">

--- a/lessons/gallery/excels/remarks_ideal.xlsx
+++ b/lessons/gallery/excels/remarks_ideal.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,14 @@
     </font>
     <font>
       <name val="Segoe UI Emoji"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -58,11 +66,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,7 +448,7 @@
     </comment>
     <comment ref="J42" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
+        <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
       </text>
     </comment>
     <comment ref="M42" authorId="0" shapeId="0">
@@ -447,7 +458,7 @@
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:35:33.317) ~0.86, -; (12:35:38.458), -Karelia (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520) ~0.67, +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
+        <t>-Karelia (12:35:33.317) ~0.86, -; (12:35:38.458), -Karelia (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520) ~0.67, +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
@@ -712,7 +723,7 @@
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
       <text>
-        <t>" (x2), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, karelia, max, muBoolean, my, orderd, t (x2), title, we, welcome (x2), Document*, log*</t>
+        <t>" (x3), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, karelia, max, muBoolean, my, orderd, t (x3), title, we, welcome (x3), Document*, log*</t>
       </text>
     </comment>
     <comment ref="H68" authorId="0" shapeId="0">
@@ -722,7 +733,7 @@
     </comment>
     <comment ref="J68" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +karelia (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
+        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +karelia (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
       </text>
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
@@ -732,7 +743,7 @@
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Karelia (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:15.871), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970) ~0.00, -Wednesday (13:36:38.686) ~0.11, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +i (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
+        <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Karelia (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -to (13:29:35.300) ~0.50, -" (13:29:36.010), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970) ~0.00, -Wednesday (13:36:38.686) ~0.11, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
@@ -1399,22 +1410,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1435,22 +1430,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1503,7 +1482,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +22 (00:00:00), +Agust (00:00:00), +KArelia (00:00:00), +Wwlcome (00:00:00), +anotherdog (00:00:00), +braeak (00:00:00), +charlie (00:00:00), +coneole (00:00:00), +const (00:00:00), +friday (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +pold (00:00:00), +tab (00:00:00), +wednesday (00:00:00), +} (00:00:00), -Tab (12:31:12.499), -Karelia (12:35:33.317), -Karelia (12:46:59.354), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066), -36 (13:30:50.077), -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881), -` (13:31:57.168), -` (13:32:14.220), -; (13:33:31.713), -August (13:33:55.549), -Wednesday (13:36:38.686), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>99.5</v>
       </c>
@@ -1520,12 +1498,11 @@
           <t>-Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.90, -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881) ~0.75, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -; (13:33:31.713), -August (13:33:55.549) ~0.83, -Wednesday (13:36:38.686) ~0.89, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736) ~0.83, +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1573,7 +1550,6 @@
           <t>+Javascript (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +welcome (00:00:00), -JavaScript (12:24:24.306), -myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -Karelia (12:46:59.354), -Karelia (13:28:16.030), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -` (13:31:57.168), -` (13:32:14.220)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>99.5</v>
       </c>
@@ -1590,12 +1566,11 @@
           <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -Karelia (12:46:59.354) ~0.86, -Karelia (13:28:16.030) ~0.86, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1612,20 +1587,6 @@
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1641,22 +1602,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1677,22 +1622,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1714,20 +1643,6 @@
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1743,22 +1658,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1779,22 +1678,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1847,7 +1730,6 @@
           <t>+  (00:00:00), +" (00:00:00), +, (00:00:00), +, (00:00:00), +1 (00:00:00), +2 (00:00:00), +3 (00:00:00), +; (00:00:00), += (00:00:00), +Agust (00:00:00), +[ (00:00:00), +] (00:00:00), +abbreaviations (00:00:00), +date (00:00:00), +karelia (00:00:00), +max (00:00:00), +myArray (00:00:00), +welcome (00:00:00), -abbreviations (12:29:01.416), -Karelia (12:35:33.317), -Max (13:05:08.613), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560), -Date (13:33:53.451), -August (13:33:55.549)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>99.5</v>
       </c>
@@ -1864,12 +1746,11 @@
           <t>-Karelia (12:35:33.317) ~0.86, -Max (13:05:08.613) ~0.67, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560) ~0.86, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,22 +1766,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1922,20 +1787,6 @@
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1951,22 +1802,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1987,22 +1822,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2023,22 +1842,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2059,22 +1862,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2127,7 +1914,6 @@
           <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +) (00:00:00), ++ (00:00:00), +, (00:00:00), +. (00:00:00), +5 (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +Charle (00:00:00), +Monday (00:00:00), +a (00:00:00), +a (00:00:00), +am (00:00:00), +b (00:00:00), +boilerpate (00:00:00), +console (00:00:00), +log (00:00:00), -! (12:24:11.928), -boilerplate (12:30:45.202), +log* (12:53:22.757), -error (12:53:23.899), -Charlie (13:07:39.223), -. (13:19:44.184), -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168), -` (13:32:14.220), -Weekend (13:37:10.693)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -2144,12 +1930,11 @@
           <t>+log* (12:53:22.757), -error (12:53:23.899), -Charlie (13:07:39.223) ~0.86, -. (13:19:44.184) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -Weekend (13:37:10.693) ~0.00, +am (00:00:00), +Charle (00:00:00), +, (00:00:00), +a (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +a (00:00:00), ++ (00:00:00), +b (00:00:00), +) (00:00:00), +; (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2165,22 +1950,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2233,7 +2002,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +- (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +03 (00:00:00), +10 (00:00:00), +2024 (00:00:00), +6 (00:00:00), +7 (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +Charley (00:00:00), +Friday (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +Saturday (00:00:00), +Thursday (00:00:00), +Wednesday (00:00:00), +` (00:00:00), +` (00:00:00), +am (00:00:00), +break (00:00:00), +break (00:00:00), +case (00:00:00), +case (00:00:00), +console (00:00:00), +console (00:00:00), +eys (00:00:00), +folowed (00:00:00), +log (00:00:00), +log (00:00:00), +max (00:00:00), +monday (00:00:00), +myBoolean (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +someDay (00:00:00), +someDay (00:00:00), +studing (00:00:00), +tusday (00:00:00), +weekend (00:00:00), -: (12:29:02.589), -followed (12:31:10.973), -study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095), -Max (13:05:08.613), -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524), -" (13:05:23.089), -" (13:05:24.754), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -" (13:07:52.850), -" (13:07:53.974), -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437), -" (13:20:07.578), -" (13:20:08.157), -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026)</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>97.8</v>
       </c>
@@ -2250,12 +2018,11 @@
           <t>-study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095) ~0.00, -Max (13:05:08.613) ~0.67, -" (13:05:08.847) ~0.00, -" (13:05:18.869) ~0.00, -" (13:05:20.541) ~0.00, -eyes (13:05:22.524) ~0.75, -" (13:05:23.089) ~0.00, -" (13:05:24.754) ~0.00, -" (13:07:37.700) ~0.00, -Charlie (13:07:39.223) ~0.71, -" (13:07:39.689) ~0.00, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -" (13:10:58.977) ~0.00, -" (13:11:00.402) ~0.00, -" (13:11:05.379) ~0.00, -" (13:11:09.329) ~0.00, -" (13:11:10.342) ~0.00, -" (13:11:12.437) ~0.00, -" (13:20:07.578) ~0.00, -" (13:20:08.157) ~0.00, -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463) ~0.00, -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019) ~0.75, -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667) ~0.75, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.71, -Thursday (13:36:45.577) ~0.44, -Friday (13:36:53.097) ~0.50, -Weekend (13:37:10.693) ~0.86, -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +, (00:00:00), +myBoolean (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2271,22 +2038,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2307,22 +2058,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2396,12 +2131,11 @@
           <t>-; (12:42:36.696), -; (12:52:14.599), -furr (13:05:18.077) ~0.75, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -+ (13:19:45.738) ~0.00, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:38.713) ~0.00, -, (13:29:49.778), -s3 (13:29:51.023), +fur (00:00:00), +' (00:00:00), +' (00:00:00), +* (00:00:00), +' (00:00:00), +' (00:00:00)</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2449,7 +2183,6 @@
           <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), ++ (00:00:00), +, (00:00:00), +, (00:00:00), +3 (00:00:00), +Container (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Id (00:00:00), +august (00:00:00), +charlie (00:00:00), +cosole (00:00:00), +emmet (00:00:00), +enter (00:00:00), +fraiday (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +javascript (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +rex (00:00:00), +tab (00:00:00), +thursday (00:00:00), +tuesday (00:00:00), +weekend (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +wendsday (00:00:00), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -id (12:27:55.052), -My (12:28:56.380), -Emmet (12:28:58.636), -HTML (12:30:43.236), -Tab (12:31:12.499), -Enter (12:31:14.293), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -at (12:35:31.858), -Karelia (12:35:33.317), -Karelia (12:46:59.354), -2 (12:48:52.350), -dog (13:05:03.658), -Max (13:05:08.613), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -Charlie (13:07:39.223), -dog (13:07:52.399), -Rex (13:11:00.170), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -I (13:30:59.741), -` (13:31:57.168), -I (13:32:08.777), -` (13:32:14.220), -August (13:33:55.549), -console (13:34:01.942), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693)</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>95.7</v>
       </c>
@@ -2466,12 +2199,11 @@
           <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -at (12:35:31.858) ~0.00, -Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -2 (12:48:52.350) ~0.00, -dog (13:05:03.658) ~0.67, -Max (13:05:08.613) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -dog (13:07:52.399) ~0.67, -Rex (13:11:00.170) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -I (13:30:59.741) ~0.00, -` (13:31:57.168) ~0.00, -I (13:32:08.777) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -console (13:34:01.942) ~0.86, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.67, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.71, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2487,22 +2219,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2523,22 +2239,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2560,20 +2260,6 @@
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2589,22 +2275,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2657,7 +2327,6 @@
           <t>+' (00:00:00), +' (00:00:00), +boilerdplate (00:00:00), +lesson (00:00:00), -Lesson (12:24:25.593), -boilerplate (12:30:45.202), -; (12:47:19.402), -` (13:31:57.168), -` (13:32:14.220)</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -2674,12 +2343,11 @@
           <t>-; (12:47:19.402), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, +' (00:00:00), +' (00:00:00)</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2748,12 +2416,11 @@
           <t>-; (13:02:35.373), -; (13:20:09.716), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -= (13:26:10.651), -; (13:26:12.162), -; (13:26:24.323), -! (13:28:16.362), -! (13:28:30.583), -36 (13:30:50.077) ~0.50, -; (13:32:15.376), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +35 (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2769,22 +2436,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2805,22 +2456,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2841,22 +2476,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2877,22 +2496,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2945,7 +2548,6 @@
           <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +/ (00:00:00), +21 (00:00:00), +Javascript (00:00:00), +anpotherDog (00:00:00), +august (00:00:00), +charlie (00:00:00), +defeault (00:00:00), +friday (00:00:00), +html (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +max (00:00:00), +monday (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +powb (00:00:00), +someData (00:00:00), +tab (00:00:00), +thrusday (00:00:00), +tuesday (00:00:00), +underdefined (00:00:00), +utf (00:00:00), +wednesday (00:00:00), +weekwnd (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), -! (12:24:11.928), -UTF (12:24:12.488), -= (12:24:13.188), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -/ (12:29:39.313), -Tab (12:31:12.499), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:35:33.317), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -. (13:07:09.027), -Charlie (13:07:39.223), -https (13:09:28.845), -anotherDog (13:10:55.220), -; (13:20:17.407), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -36 (13:30:50.077), -; (13:31:07.806), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -August (13:33:55.549), -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -Weekend (13:37:10.693), -break (13:38:10.544), -; (13:38:10.869)</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>95.7</v>
       </c>
@@ -2962,12 +2564,11 @@
           <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:35:33.317) ~0.86, -undefined (12:43:17.799) ~0.75, -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -. (13:07:09.027) ~0.00, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.91, -; (13:20:17.407), -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -August (13:33:55.549) ~0.83, -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.62, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967) ~0.88, -Weekend (13:37:10.693) ~0.71, -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +  (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +/ (00:00:00)</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2983,22 +2584,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3019,22 +2604,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3055,22 +2624,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3091,22 +2644,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3159,7 +2696,6 @@
           <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), ++ (00:00:00), +, (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +123456 (00:00:00), +5 (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +&gt; (00:00:00), +Black (00:00:00), +Black (00:00:00), +Boolean (00:00:00), +Brown (00:00:00), +ENter (00:00:00), +JS (00:00:00), +Kaali (00:00:00), +MyBoolean (00:00:00), +Number (00:00:00), +a (00:00:00), +a (00:00:00), +a (00:00:00), +appendchild (00:00:00), +are (00:00:00), +are (00:00:00), +automatically (00:00:00), +characters (00:00:00), +console (00:00:00), +contain (00:00:00), +container (00:00:00), +cript (00:00:00), +document (00:00:00), +for (00:00:00), +getElementById (00:00:00), +global (00:00:00), +ids (00:00:00), +invalid (00:00:00), +javaScript (00:00:00), +lesson (00:00:00), +like (00:00:00), +log (00:00:00), +my (00:00:00), +myArray (00:00:00), +mynumber (00:00:00), +mystring (00:00:00), +names (00:00:00), +names (00:00:00), +need (00:00:00), +no (00:00:00), +numbers (00:00:00), +opposite (00:00:00), +oppositeboolean (00:00:00), +or (00:00:00), +spaces (00:00:00), +special (00:00:00), +start (00:00:00), +string (00:00:00), +that (00:00:00), +valid (00:00:00), +variables (00:00:00), +with (00:00:00), -&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095), -" (13:05:08.847), -black (13:05:20.120), -brown (13:05:24.043), -; (13:07:10.952), -Charlie (13:07:39.223), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -black (13:11:11.856), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>23.4</v>
       </c>
@@ -3176,12 +2712,11 @@
           <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095) ~0.00, -" (13:05:08.847) ~0.00, -black (13:05:20.120) ~0.80, -brown (13:05:24.043) ~0.80, -; (13:07:10.952), -Charlie (13:07:39.223) ~0.43, -black (13:11:11.856) ~0.80, -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3226,10 +2761,9 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
+        </is>
+      </c>
       <c r="M42" t="n">
         <v>96.2</v>
       </c>
@@ -3243,15 +2777,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-Karelia (12:35:33.317) ~0.86, -; (12:35:38.458), -Karelia (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520) ~0.67, +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
+          <t>-Karelia (12:35:33.317) ~0.86, -; (12:35:38.458), -Karelia (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520) ~0.67, +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3267,22 +2800,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3303,22 +2820,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3371,7 +2872,6 @@
           <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +Charle (00:00:00), +abbreviation (00:00:00), +august (00:00:00), +friday (00:00:00), +getDate (00:00:00), +karelia (00:00:00), +max (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +orderlist (00:00:00), +thursday (00:00:00), +tuesday (00:00:00), +viewpoint (00:00:00), +wednesday (00:00:00), +weekend (00:00:00), -viewport (12:24:12.738), -abbreviations (12:29:01.416), -ordered (12:31:02.226), -list (12:31:03.447), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:46:59.354), -Max (13:05:08.613), -Charlie (13:07:39.223), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -getDay (13:34:50.180), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>97.3</v>
       </c>
@@ -3388,12 +2888,11 @@
           <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -Charlie (13:07:39.223) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -getDay (13:34:50.180) ~0.71, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.83, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3441,7 +2940,6 @@
           <t>+Furr (00:00:00), +Html (00:00:00), +Kareliaa (00:00:00), +Lession (00:00:00), +defult (00:00:00), +year (00:00:00), -Lesson (12:24:25.593), -HTML (12:30:43.236), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818), -default (13:37:00.967)</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -3458,12 +2956,11 @@
           <t>-Karelia (12:46:59.354) ~0.88, +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077) ~0.75, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818) ~0.80, -default (13:37:00.967) ~0.86, +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3480,20 +2977,6 @@
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3541,7 +3024,6 @@
           <t>+" (00:00:00), +" (00:00:00), +Agust (00:00:00), +Karelia (00:00:00), +Numbers (00:00:00), +Viewport (00:00:00), +charlie (00:00:00), +comsole (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +intial (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +order (00:00:00), -viewport (12:24:12.738), -initial (12:24:13.118), -Lesson (12:24:25.593), -/ (12:29:39.313), -ordered (12:31:02.226), -Charlie (13:07:39.223), -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678)</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>97.3</v>
       </c>
@@ -3558,12 +3040,11 @@
           <t>-Charlie (13:07:39.223) ~0.86, -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066) ~0.86, -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3579,22 +3060,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3647,7 +3112,6 @@
           <t>+% (00:00:00), +, (00:00:00), +, (00:00:00), +1 (00:00:00), +2 (00:00:00), +3 (00:00:00), +5 (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +case (00:00:00), +enter (00:00:00), +myArray (00:00:00), +viewpoint (00:00:00), -viewport (12:24:12.738), -Enter (12:31:14.293), -; (12:35:38.458), -; (12:41:10.990), +log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053), -default (13:37:00.967)</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -3664,12 +3128,11 @@
           <t>-; (12:35:38.458), -; (12:41:10.990), +log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053) ~0.00, -default (13:37:00.967) ~0.14, +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3738,12 +3201,11 @@
           <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030) ~0.86, -36 (13:30:50.077) ~0.00, +Karela (00:00:00), +22 (00:00:00)</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3759,22 +3221,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3795,22 +3241,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3831,22 +3261,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3867,22 +3281,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3935,7 +3333,6 @@
           <t>+" (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +) (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +. (00:00:00), +19 (00:00:00), +2006 (00:00:00), +28 (00:00:00), +4 (00:00:00), +5 (00:00:00), +55 (00:00:00), +67 (00:00:00), +67 (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +December (00:00:00), +Hello (00:00:00), +Hello (00:00:00), +XXX (00:00:00), +Years (00:00:00), +a (00:00:00), +console (00:00:00), +const (00:00:00), +containter (00:00:00), +item (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +log (00:00:00), +rex (00:00:00), -container (12:30:48.969), -items (12:31:06.206), -25 (12:33:49.617), -2 (12:33:50.650), -; (12:36:56.445), -Karelia (12:46:59.354), -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170), -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030), -! (13:28:16.362), -Karelia (13:28:30.418), -! (13:28:30.583), -" (13:29:31.463), -Karelia (13:29:38.066), -36 (13:30:50.077), -years (13:32:12.609), -; (13:32:15.376), -August (13:33:55.549), -24 (13:33:56.247), -2025 (13:33:58.460)</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -3952,12 +3349,11 @@
           <t>-25 (12:33:49.617) ~0.00, -2 (12:33:50.650) ~0.00, -; (12:36:56.445), -Karelia (12:46:59.354) ~0.00, -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170) ~0.67, -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -" (13:29:31.463) ~0.00, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:32:12.609) ~0.80, -; (13:32:15.376), -August (13:33:55.549) ~0.00, -24 (13:33:56.247) ~0.50, -2025 (13:33:58.460) ~0.50, +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q56" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3973,22 +3369,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4009,22 +3389,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4077,7 +3441,6 @@
           <t>+" (00:00:00), +" (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +Console (00:00:00), +SomeDate (00:00:00), +abbreviation (00:00:00), +karelia (00:00:00), +toady (00:00:00), -abbreviations (12:29:01.416), -Karelia (12:46:59.354), -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097)</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>99.5</v>
       </c>
@@ -4094,12 +3457,11 @@
           <t>-Karelia (12:46:59.354) ~0.86, -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +karelia (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q59" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4115,22 +3477,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4183,7 +3529,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +. (00:00:00), +. (00:00:00), +142 (00:00:00), +; (00:00:00), +; (00:00:00), +Console (00:00:00), +First (00:00:00), +Math (00:00:00), +Ordered (00:00:00), +a (00:00:00), +appendchild (00:00:00), +b (00:00:00), +connstmyString (00:00:00), +consloe (00:00:00), +console (00:00:00), +java (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +log (00:00:00), +max (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +pow (00:00:00), +script (00:00:00), +tab (00:00:00), +year (00:00:00), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -first (12:28:57.481), -! (12:30:40.873), -ordered (12:31:02.226), -Tab (12:31:12.499), -myNumber (12:33:44.402), -console (12:33:56.141), -myNumber (12:33:59.949), -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317), -! (12:42:04.755), -42 (12:42:11.528), -console (12:43:10.202), -Karelia (12:46:59.354), -Max (13:05:08.613), -appendChild (13:13:30.342), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -Karelia (13:29:38.066), -years (13:32:12.609), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>95.7</v>
       </c>
@@ -4200,12 +3545,11 @@
           <t>-myNumber (12:33:44.402) ~0.88, -console (12:33:56.141) ~0.71, -myNumber (12:33:59.949) ~0.88, -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317) ~0.86, -! (12:42:04.755), -42 (12:42:11.528) ~0.67, -console (12:43:10.202) ~0.86, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -appendChild (13:13:30.342) ~0.91, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -Karelia (13:29:38.066) ~0.86, -years (13:32:12.609) ~0.80, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4253,7 +3597,6 @@
           <t>+48 (00:00:00), +Lession (00:00:00), +bolierplate (00:00:00), +brows (00:00:00), +enter (00:00:00), +tab (00:00:00), -Lesson (12:24:25.593), -boilerplate (12:30:45.202), -Tab (12:31:12.499), -Enter (12:31:14.293), -; (12:35:38.458), -brown (13:05:24.043), -; (13:12:34.331), -; (13:28:31.528), -36 (13:30:50.077), -; (13:34:00.044)</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
         <v>97.8</v>
       </c>
@@ -4270,12 +3613,11 @@
           <t>-; (12:35:38.458), -brown (13:05:24.043) ~0.80, -; (13:12:34.331), -; (13:28:31.528), -36 (13:30:50.077) ~0.00, -; (13:34:00.044), +brows (00:00:00), +48 (00:00:00)</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q62" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4291,22 +3633,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4327,22 +3653,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4363,22 +3673,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4431,7 +3725,6 @@
           <t>+" (00:00:00), +( (00:00:00), +) (00:00:00), +. (00:00:00), +CONSOLE (00:00:00), +Html (00:00:00), +LOG (00:00:00), +Math (00:00:00), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +order (00:00:00), +pow (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -HTML (12:30:43.236), -ordered (12:31:02.226), -oppositeBoolean (12:41:07.806), -oppositeBoolean (12:41:21.351), +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029), -log (13:19:44.775), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699)</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
         <v>97.3</v>
       </c>
@@ -4448,12 +3741,11 @@
           <t>-oppositeBoolean (12:41:07.806) ~0.93, -oppositeBoolean (12:41:21.351) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029) ~0.00, -log (13:19:44.775) ~0.00, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Q66" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4469,22 +3761,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4511,11 +3787,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>" (x2), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, karelia, max, muBoolean, my, orderd, t (x2), title, we, welcome (x2), Document*, log*</t>
+          <t>" (x3), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, karelia, max, muBoolean, my, orderd, t (x3), title, we, welcome (x3), Document*, log*</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4530,14 +3806,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>89.7</v>
+        <v>89.2</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +karelia (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
+          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +karelia (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
+        </is>
+      </c>
       <c r="M68" t="n">
         <v>87.5</v>
       </c>
@@ -4547,19 +3822,18 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>90.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Karelia (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:15.871), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970) ~0.00, -Wednesday (13:36:38.686) ~0.11, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +i (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
+          <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Karelia (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -to (13:29:35.300) ~0.50, -" (13:29:36.010), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970) ~0.00, -Wednesday (13:36:38.686) ~0.11, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4575,22 +3849,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4643,7 +3901,6 @@
           <t>+" (00:00:00), +, (00:00:00), +, (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +22 (00:00:00), +Console (00:00:00), +MAX (00:00:00), +aage (00:00:00), +anoherDog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +muBoolean (00:00:00), +muNumber (00:00:00), +weelend (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +´ (00:00:00), +´ (00:00:00), -Lesson (12:24:25.593), -! (12:30:40.873), -myNumber (12:33:44.402), -myBoolean (12:36:27.967), -Karelia (12:46:59.354), -. (12:58:07.899), -; (13:02:35.373), -Max (13:05:08.613), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -age (13:30:48.674), -36 (13:30:50.077), -` (13:32:14.220), -; (13:32:15.376), -console (13:34:46.231), -} (13:35:58.376), -Weekend (13:37:10.693), -; (13:38:10.869)</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
         <v>97.8</v>
       </c>
@@ -4660,12 +3917,11 @@
           <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -Karelia (12:46:59.354) ~0.86, -. (12:58:07.899) ~0.00, -; (13:02:35.373) ~0.00, -Max (13:05:08.613) ~0.33, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010), -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -36 (13:30:50.077) ~0.00, -` (13:32:14.220) ~0.00, -; (13:32:15.376), -console (13:34:46.231) ~0.86, -} (13:35:58.376), -Weekend (13:37:10.693) ~0.71, -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4689,7 +3945,6 @@
       <c r="E71" t="n">
         <v>0</v>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>99.90000000000001</v>
       </c>
@@ -4709,11 +3964,9 @@
           <t>-" (13:29:13.699)</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
         <v>100</v>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
         <v>99.90000000000001</v>
       </c>
@@ -4722,12 +3975,11 @@
           <t>-" (13:29:13.699)</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q71" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4775,7 +4027,6 @@
           <t>+22 (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +studt (00:00:00), +todat (00:00:00), +viewpoint (00:00:00), +year (00:00:00), -viewport (12:24:12.738), -study (12:35:31.258), -Karelia (12:35:33.317), -36 (13:30:50.077), -years (13:31:05.818), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
         <v>99.5</v>
       </c>
@@ -4792,12 +4043,11 @@
           <t>-study (12:35:31.258) ~0.80, -Karelia (12:35:33.317) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:31:05.818) ~0.80, -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q72" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4845,7 +4095,6 @@
           <t>+21 (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -36 (13:30:50.077)</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>98.40000000000001</v>
       </c>
@@ -4862,12 +4111,11 @@
           <t>-36 (13:30:50.077) ~0.00, +21 (00:00:00)</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q73" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4883,22 +4131,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4951,7 +4183,6 @@
           <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +HTMl (00:00:00), +browen (00:00:00), +charlie (00:00:00), +friday (00:00:00), +getday (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +saturday (00:00:00), +tab (00:00:00), +thursday (00:00:00), +today (00:00:00), +tuesday (00:00:00), +underfined (00:00:00), +view (00:00:00), +yeasrs (00:00:00), -viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), -myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
         <v>97.3</v>
       </c>
@@ -4968,12 +4199,11 @@
           <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108), -myBoolean (12:41:00.416) ~0.89, -; (12:41:04.494), -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, -Karelia (12:46:59.354) ~0.86, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613) ~0.67, -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -; (13:26:07.158), -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759) ~0.00, -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -years (13:32:12.609) ~0.83, -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019) ~0.25, -getDay (13:35:54.315) ~0.83, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.44, -Thursday (13:36:45.577) ~0.50, -Friday (13:36:53.097) ~0.38, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +today (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q75" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4989,22 +4219,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5025,22 +4239,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5080,7 +4278,6 @@
       <c r="H78" t="n">
         <v>100</v>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -5089,7 +4286,6 @@
           <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +, (00:00:00), +26 (00:00:00), +HTML (00:00:00), +Javascript (00:00:00), +Mondayy (00:00:00), +allowed (00:00:00), +lig (00:00:00), +oppositeBolean (00:00:00), -html (12:24:12.048), -JavaScript (12:24:24.306), -followed (12:31:10.973), -log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -36 (13:30:50.077), -Monday (13:36:18.214), -; (13:38:17.969)</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
         <v>96.7</v>
       </c>
@@ -5106,12 +4302,11 @@
           <t>-log (12:35:41.570) ~0.67, -oppositeBoolean (12:36:43.817) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -36 (13:30:50.077) ~0.50, -Monday (13:36:18.214) ~0.86, -; (13:38:17.969) ~0.00, +lig (00:00:00), +oppositeBolean (00:00:00), +26 (00:00:00), +Mondayy (00:00:00), +, (00:00:00)</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="Q78" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5159,7 +4354,6 @@
           <t>+! (00:00:00), +&amp; (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +. (00:00:00), +. (00:00:00), +31 (00:00:00), +; (00:00:00), +All (00:00:00), +console (00:00:00), +getDay (00:00:00), +log (00:00:00), +old (00:00:00), +someDate (00:00:00), -ol (12:30:53.144), -all (12:31:09.440), -; (13:05:06.814), -% (13:22:03.842), -36 (13:30:50.077)</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -5176,12 +4370,11 @@
           <t>-; (13:05:06.814), -% (13:22:03.842) ~0.00, -36 (13:30:50.077) ~0.50, +&amp; (00:00:00), +! (00:00:00), +31 (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +someDate (00:00:00), +. (00:00:00), +getDay (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="Q79" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5197,22 +4390,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5286,12 +4463,11 @@
           <t>-ABC (12:42:20.731) ~0.00, -; (13:02:35.373), -Welcome (13:28:13.560) ~0.86, -Welcome (13:28:27.998) ~0.86, -Welcome (13:29:34.675) ~0.86, -36 (13:30:50.077) ~0.00, +abc (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +20 (00:00:00)</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q81" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5339,11 +4515,9 @@
           <t>+21 (00:00:00), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), -ABC (12:42:20.731), -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354), -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077), -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077), -; (13:31:07.806), -; (13:32:15.376)</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
         <v>100</v>
       </c>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
         <v>98</v>
       </c>
@@ -5352,12 +4526,11 @@
           <t>-ABC (12:42:20.731) ~0.00, -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354) ~0.00, -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077) ~0.75, -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q82" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5405,7 +4578,6 @@
           <t>+; (00:00:00), +Thrusday (00:00:00), +enter (00:00:00), +orderd (00:00:00), +somedate (00:00:00), +tab (00:00:00), -: (12:29:02.589), -ordered (12:31:02.226), -Tab (12:31:12.499), -Enter (12:31:14.293), -; (12:47:24.675), +log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667), -Thursday (13:36:45.577)</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>97.8</v>
       </c>
@@ -5422,12 +4594,11 @@
           <t>-; (12:47:24.675), +log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667) ~0.88, -Thursday (13:36:45.577) ~0.75, +somedate (00:00:00), +Thrusday (00:00:00)</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="Q83" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5443,22 +4614,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5479,22 +4634,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5516,20 +4655,6 @@
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
       <c r="T86" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5551,20 +4676,6 @@
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
       <c r="T87" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5586,20 +4697,6 @@
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
       <c r="T88" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5621,20 +4718,6 @@
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
       <c r="T89" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5656,20 +4739,6 @@
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
       <c r="T90" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5691,20 +4760,6 @@
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
       <c r="T91" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5726,20 +4781,6 @@
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
       <c r="T92" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5761,20 +4802,6 @@
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
       <c r="T93" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5796,20 +4823,6 @@
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
       <c r="T94" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5831,20 +4844,6 @@
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
       <c r="T95" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5866,20 +4865,6 @@
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
       <c r="T96" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5901,20 +4886,6 @@
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
       <c r="T97" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5936,20 +4907,6 @@
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
       <c r="T98" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5971,20 +4928,6 @@
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
       <c r="T99" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6006,20 +4949,6 @@
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
       <c r="T100" t="inlineStr">
         <is>
           <t>LLM</t>

--- a/lessons/gallery/excels/remarks_ideal.xlsx
+++ b/lessons/gallery/excels/remarks_ideal.xlsx
@@ -158,7 +158,7 @@
   <commentList>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>" (x4), 22, Agust, KArelia, Wwlcome, anotherdog, braeak, charlie, coneole, const, friday, karelia (x4), pold, tab, wednesday, }</t>
+        <t>" (x4), 22, Agust, ACademy, Wwlcome, anotherdog, braeak, charlie, coneole, const, friday, academy (x4), pold, tab, wednesday, }</t>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
@@ -168,7 +168,7 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +22 (00:00:00), +Agust (00:00:00), +KArelia (00:00:00), +Wwlcome (00:00:00), +anotherdog (00:00:00), +braeak (00:00:00), +charlie (00:00:00), +coneole (00:00:00), +const (00:00:00), +friday (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +pold (00:00:00), +tab (00:00:00), +wednesday (00:00:00), +} (00:00:00), -Tab (12:31:12.499), -Karelia (12:35:33.317), -Karelia (12:46:59.354), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066), -36 (13:30:50.077), -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881), -` (13:31:57.168), -` (13:32:14.220), -; (13:33:31.713), -August (13:33:55.549), -Wednesday (13:36:38.686), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736)</t>
+        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +22 (00:00:00), +Agust (00:00:00), +ACademy (00:00:00), +Wwlcome (00:00:00), +anotherdog (00:00:00), +braeak (00:00:00), +charlie (00:00:00), +coneole (00:00:00), +const (00:00:00), +friday (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +pold (00:00:00), +tab (00:00:00), +wednesday (00:00:00), +} (00:00:00), -Tab (12:31:12.499), -Academy (12:35:33.317), -Academy (12:46:59.354), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -Welcome (13:28:13.560), -Academy (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Academy (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Academy (13:29:38.066), -36 (13:30:50.077), -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881), -` (13:31:57.168), -` (13:32:14.220), -; (13:33:31.713), -August (13:33:55.549), -Wednesday (13:36:38.686), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736)</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
@@ -178,12 +178,12 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.90, -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881) ~0.75, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -; (13:33:31.713), -August (13:33:55.549) ~0.83, -Wednesday (13:36:38.686) ~0.89, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736) ~0.83, +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
+        <t>-Academy (12:35:33.317) ~0.86, -Academy (12:46:59.354) ~0.86, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.90, -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -Welcome (13:28:13.560) ~0.86, -Academy (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Academy (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Academy (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881) ~0.75, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -; (13:33:31.713), -August (13:33:55.549) ~0.83, -Wednesday (13:36:38.686) ~0.89, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736) ~0.83, +const (00:00:00), +academy (00:00:00), +academy (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +ACademy (00:00:00), +" (00:00:00), +academy (00:00:00), +" (00:00:00), +academy (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
       <text>
-        <t>Javascript, karelia (x4), mystring (x2), welcome</t>
+        <t>Javascript, academy (x4), mystring (x2), welcome</t>
       </text>
     </comment>
     <comment ref="H5" authorId="0" shapeId="0">
@@ -193,7 +193,7 @@
     </comment>
     <comment ref="J5" authorId="0" shapeId="0">
       <text>
-        <t>+Javascript (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +welcome (00:00:00), -JavaScript (12:24:24.306), -myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -Karelia (12:46:59.354), -Karelia (13:28:16.030), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -` (13:31:57.168), -` (13:32:14.220)</t>
+        <t>+Javascript (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +welcome (00:00:00), -JavaScript (12:24:24.306), -myString (12:35:27.676), -Academy (12:35:33.317), -myString (12:35:43.276), -Academy (12:46:59.354), -Academy (13:28:16.030), -Welcome (13:28:27.998), -Academy (13:28:30.418), -` (13:31:57.168), -` (13:32:14.220)</t>
       </text>
     </comment>
     <comment ref="M5" authorId="0" shapeId="0">
@@ -203,7 +203,7 @@
     </comment>
     <comment ref="O5" authorId="0" shapeId="0">
       <text>
-        <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -Karelia (12:46:59.354) ~0.86, -Karelia (13:28:16.030) ~0.86, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
+        <t>-myString (12:35:27.676) ~0.88, -Academy (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -Academy (12:46:59.354) ~0.86, -Academy (13:28:16.030) ~0.86, -Welcome (13:28:27.998) ~0.86, -Academy (13:28:30.418) ~0.86, -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +academy (00:00:00), +mystring (00:00:00), +academy (00:00:00), +academy (00:00:00), +welcome (00:00:00), +academy (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D12" authorId="0" shapeId="0">
@@ -213,7 +213,7 @@
     </comment>
     <comment ref="E12" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve"> , ", , (x2), 1, 2, 3, ;, =, Agust, [, ], abbreaviations, date, karelia, max, myArray, welcome</t>
+        <t xml:space="preserve"> , ", , (x2), 1, 2, 3, ;, =, Agust, [, ], abbreaviations, date, academy, max, myArray, welcome</t>
       </text>
     </comment>
     <comment ref="H12" authorId="0" shapeId="0">
@@ -223,7 +223,7 @@
     </comment>
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
-        <t>+  (00:00:00), +" (00:00:00), +, (00:00:00), +, (00:00:00), +1 (00:00:00), +2 (00:00:00), +3 (00:00:00), +; (00:00:00), += (00:00:00), +Agust (00:00:00), +[ (00:00:00), +] (00:00:00), +abbreaviations (00:00:00), +date (00:00:00), +karelia (00:00:00), +max (00:00:00), +myArray (00:00:00), +welcome (00:00:00), -abbreviations (12:29:01.416), -Karelia (12:35:33.317), -Max (13:05:08.613), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560), -Date (13:33:53.451), -August (13:33:55.549)</t>
+        <t>+  (00:00:00), +" (00:00:00), +, (00:00:00), +, (00:00:00), +1 (00:00:00), +2 (00:00:00), +3 (00:00:00), +; (00:00:00), += (00:00:00), +Agust (00:00:00), +[ (00:00:00), +] (00:00:00), +abbreaviations (00:00:00), +date (00:00:00), +academy (00:00:00), +max (00:00:00), +myArray (00:00:00), +welcome (00:00:00), -abbreviations (12:29:01.416), -Academy (12:35:33.317), -Max (13:05:08.613), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560), -Date (13:33:53.451), -August (13:33:55.549)</t>
       </text>
     </comment>
     <comment ref="M12" authorId="0" shapeId="0">
@@ -233,7 +233,7 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:35:33.317) ~0.86, -Max (13:05:08.613) ~0.67, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560) ~0.86, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
+        <t>-Academy (12:35:33.317) ~0.86, -Max (13:05:08.613) ~0.67, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560) ~0.86, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +academy (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -273,7 +273,7 @@
     </comment>
     <comment ref="J21" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +- (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +03 (00:00:00), +10 (00:00:00), +2024 (00:00:00), +6 (00:00:00), +7 (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +Charley (00:00:00), +Friday (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +Saturday (00:00:00), +Thursday (00:00:00), +Wednesday (00:00:00), +` (00:00:00), +` (00:00:00), +am (00:00:00), +break (00:00:00), +break (00:00:00), +case (00:00:00), +case (00:00:00), +console (00:00:00), +console (00:00:00), +eys (00:00:00), +folowed (00:00:00), +log (00:00:00), +log (00:00:00), +max (00:00:00), +monday (00:00:00), +myBoolean (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +someDay (00:00:00), +someDay (00:00:00), +studing (00:00:00), +tusday (00:00:00), +weekend (00:00:00), -: (12:29:02.589), -followed (12:31:10.973), -study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095), -Max (13:05:08.613), -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524), -" (13:05:23.089), -" (13:05:24.754), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -" (13:07:52.850), -" (13:07:53.974), -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437), -" (13:20:07.578), -" (13:20:08.157), -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026)</t>
+        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +- (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +03 (00:00:00), +10 (00:00:00), +2024 (00:00:00), +6 (00:00:00), +7 (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +Charley (00:00:00), +Friday (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +Saturday (00:00:00), +Thursday (00:00:00), +Wednesday (00:00:00), +` (00:00:00), +` (00:00:00), +am (00:00:00), +break (00:00:00), +break (00:00:00), +case (00:00:00), +case (00:00:00), +console (00:00:00), +console (00:00:00), +eys (00:00:00), +folowed (00:00:00), +log (00:00:00), +log (00:00:00), +max (00:00:00), +monday (00:00:00), +myBoolean (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +someDay (00:00:00), +someDay (00:00:00), +studing (00:00:00), +tusday (00:00:00), +weekend (00:00:00), -: (12:29:02.589), -followed (12:31:10.973), -study (12:35:31.258), -at (12:35:31.858), -Academy (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095), -Max (13:05:08.613), -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524), -" (13:05:23.089), -" (13:05:24.754), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -" (13:07:52.850), -" (13:07:53.974), -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437), -" (13:20:07.578), -" (13:20:08.157), -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026)</t>
       </text>
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
@@ -283,7 +283,7 @@
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
       <text>
-        <t>-study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095) ~0.00, -Max (13:05:08.613) ~0.67, -" (13:05:08.847) ~0.00, -" (13:05:18.869) ~0.00, -" (13:05:20.541) ~0.00, -eyes (13:05:22.524) ~0.75, -" (13:05:23.089) ~0.00, -" (13:05:24.754) ~0.00, -" (13:07:37.700) ~0.00, -Charlie (13:07:39.223) ~0.71, -" (13:07:39.689) ~0.00, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -" (13:10:58.977) ~0.00, -" (13:11:00.402) ~0.00, -" (13:11:05.379) ~0.00, -" (13:11:09.329) ~0.00, -" (13:11:10.342) ~0.00, -" (13:11:12.437) ~0.00, -" (13:20:07.578) ~0.00, -" (13:20:08.157) ~0.00, -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463) ~0.00, -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019) ~0.75, -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667) ~0.75, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.71, -Thursday (13:36:45.577) ~0.44, -Friday (13:36:53.097) ~0.50, -Weekend (13:37:10.693) ~0.86, -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +, (00:00:00), +myBoolean (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
+        <t>-study (12:35:31.258), -at (12:35:31.858), -Academy (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095) ~0.00, -Max (13:05:08.613) ~0.67, -" (13:05:08.847) ~0.00, -" (13:05:18.869) ~0.00, -" (13:05:20.541) ~0.00, -eyes (13:05:22.524) ~0.75, -" (13:05:23.089) ~0.00, -" (13:05:24.754) ~0.00, -" (13:07:37.700) ~0.00, -Charlie (13:07:39.223) ~0.71, -" (13:07:39.689) ~0.00, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -" (13:10:58.977) ~0.00, -" (13:11:00.402) ~0.00, -" (13:11:05.379) ~0.00, -" (13:11:09.329) ~0.00, -" (13:11:10.342) ~0.00, -" (13:11:12.437) ~0.00, -" (13:20:07.578) ~0.00, -" (13:20:08.157) ~0.00, -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463) ~0.00, -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019) ~0.75, -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667) ~0.75, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.71, -Thursday (13:36:45.577) ~0.44, -Friday (13:36:53.097) ~0.50, -Weekend (13:37:10.693) ~0.86, -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +, (00:00:00), +myBoolean (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
@@ -313,7 +313,7 @@
     </comment>
     <comment ref="E25" authorId="0" shapeId="0">
       <text>
-        <t>" (x2), ' (x2), +, , (x2), 3, Container, Dog (x6), Id, august, charlie, cosole, emmet, enter, fraiday, html, i (x2), in, javascript, karelia (x5), lesson, math (x3), max, monday, my, mynumber (x2), rex, tab, thursday, tuesday, weekend, welcome (x3), wendsday</t>
+        <t>" (x2), ' (x2), +, , (x2), 3, Container, Dog (x6), Id, august, charlie, cosole, emmet, enter, fraiday, html, i (x2), in, javascript, academy (x5), lesson, math (x3), max, monday, my, mynumber (x2), rex, tab, thursday, tuesday, weekend, welcome (x3), wendsday</t>
       </text>
     </comment>
     <comment ref="H25" authorId="0" shapeId="0">
@@ -323,7 +323,7 @@
     </comment>
     <comment ref="J25" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), ++ (00:00:00), +, (00:00:00), +, (00:00:00), +3 (00:00:00), +Container (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Id (00:00:00), +august (00:00:00), +charlie (00:00:00), +cosole (00:00:00), +emmet (00:00:00), +enter (00:00:00), +fraiday (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +javascript (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +rex (00:00:00), +tab (00:00:00), +thursday (00:00:00), +tuesday (00:00:00), +weekend (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +wendsday (00:00:00), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -id (12:27:55.052), -My (12:28:56.380), -Emmet (12:28:58.636), -HTML (12:30:43.236), -Tab (12:31:12.499), -Enter (12:31:14.293), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -at (12:35:31.858), -Karelia (12:35:33.317), -Karelia (12:46:59.354), -2 (12:48:52.350), -dog (13:05:03.658), -Max (13:05:08.613), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -Charlie (13:07:39.223), -dog (13:07:52.399), -Rex (13:11:00.170), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -I (13:30:59.741), -` (13:31:57.168), -I (13:32:08.777), -` (13:32:14.220), -August (13:33:55.549), -console (13:34:01.942), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693)</t>
+        <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), ++ (00:00:00), +, (00:00:00), +, (00:00:00), +3 (00:00:00), +Container (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Id (00:00:00), +august (00:00:00), +charlie (00:00:00), +cosole (00:00:00), +emmet (00:00:00), +enter (00:00:00), +fraiday (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +javascript (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +lesson (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +rex (00:00:00), +tab (00:00:00), +thursday (00:00:00), +tuesday (00:00:00), +weekend (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +wendsday (00:00:00), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -id (12:27:55.052), -My (12:28:56.380), -Emmet (12:28:58.636), -HTML (12:30:43.236), -Tab (12:31:12.499), -Enter (12:31:14.293), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -at (12:35:31.858), -Academy (12:35:33.317), -Academy (12:46:59.354), -2 (12:48:52.350), -dog (13:05:03.658), -Max (13:05:08.613), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -Charlie (13:07:39.223), -dog (13:07:52.399), -Rex (13:11:00.170), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -Welcome (13:28:13.560), -Academy (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Academy (13:29:38.066), -I (13:30:59.741), -` (13:31:57.168), -I (13:32:08.777), -` (13:32:14.220), -August (13:33:55.549), -console (13:34:01.942), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693)</t>
       </text>
     </comment>
     <comment ref="M25" authorId="0" shapeId="0">
@@ -333,7 +333,7 @@
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -at (12:35:31.858) ~0.00, -Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -2 (12:48:52.350) ~0.00, -dog (13:05:03.658) ~0.67, -Max (13:05:08.613) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -dog (13:07:52.399) ~0.67, -Rex (13:11:00.170) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -I (13:30:59.741) ~0.00, -` (13:31:57.168) ~0.00, -I (13:32:08.777) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -console (13:34:01.942) ~0.86, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.67, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.71, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -at (12:35:31.858) ~0.00, -Academy (12:35:33.317) ~0.86, -Academy (12:46:59.354) ~0.86, -2 (12:48:52.350) ~0.00, -dog (13:05:03.658) ~0.67, -Max (13:05:08.613) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -dog (13:07:52.399) ~0.67, -Rex (13:11:00.170) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -Welcome (13:28:13.560) ~0.86, -Academy (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Academy (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Academy (13:29:38.066) ~0.86, -I (13:30:59.741) ~0.00, -` (13:31:57.168) ~0.00, -I (13:32:08.777) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -console (13:34:01.942) ~0.86, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.67, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.71, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +academy (00:00:00), +, (00:00:00), +academy (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +academy (00:00:00), +" (00:00:00), +welcome (00:00:00), +academy (00:00:00), +" (00:00:00), +welcome (00:00:00), +academy (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -388,7 +388,7 @@
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve"> , " (x2), ' (x2), , (x4), -, /, 21, Javascript, anpotherDog, august, charlie, defeault, friday, html, karelia (x4), lesson, max, monday, mynumber (x2), powb, someData, tab, thrusday, tuesday, underdefined, utf, wednesday, weekwnd, welcome (x3), log*</t>
+        <t xml:space="preserve"> , " (x2), ' (x2), , (x4), -, /, 21, Javascript, anpotherDog, august, charlie, defeault, friday, html, academy (x4), lesson, max, monday, mynumber (x2), powb, someData, tab, thrusday, tuesday, underdefined, utf, wednesday, weekwnd, welcome (x3), log*</t>
       </text>
     </comment>
     <comment ref="H36" authorId="0" shapeId="0">
@@ -398,7 +398,7 @@
     </comment>
     <comment ref="J36" authorId="0" shapeId="0">
       <text>
-        <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +/ (00:00:00), +21 (00:00:00), +Javascript (00:00:00), +anpotherDog (00:00:00), +august (00:00:00), +charlie (00:00:00), +defeault (00:00:00), +friday (00:00:00), +html (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +max (00:00:00), +monday (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +powb (00:00:00), +someData (00:00:00), +tab (00:00:00), +thrusday (00:00:00), +tuesday (00:00:00), +underdefined (00:00:00), +utf (00:00:00), +wednesday (00:00:00), +weekwnd (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), -! (12:24:11.928), -UTF (12:24:12.488), -= (12:24:13.188), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -/ (12:29:39.313), -Tab (12:31:12.499), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:35:33.317), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -. (13:07:09.027), -Charlie (13:07:39.223), -https (13:09:28.845), -anotherDog (13:10:55.220), -; (13:20:17.407), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -36 (13:30:50.077), -; (13:31:07.806), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -August (13:33:55.549), -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -Weekend (13:37:10.693), -break (13:38:10.544), -; (13:38:10.869)</t>
+        <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +/ (00:00:00), +21 (00:00:00), +Javascript (00:00:00), +anpotherDog (00:00:00), +august (00:00:00), +charlie (00:00:00), +defeault (00:00:00), +friday (00:00:00), +html (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +lesson (00:00:00), +max (00:00:00), +monday (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +powb (00:00:00), +someData (00:00:00), +tab (00:00:00), +thrusday (00:00:00), +tuesday (00:00:00), +underdefined (00:00:00), +utf (00:00:00), +wednesday (00:00:00), +weekwnd (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), -! (12:24:11.928), -UTF (12:24:12.488), -= (12:24:13.188), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -/ (12:29:39.313), -Tab (12:31:12.499), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -Academy (12:35:33.317), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -. (13:07:09.027), -Charlie (13:07:39.223), -https (13:09:28.845), -anotherDog (13:10:55.220), -; (13:20:17.407), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560), -Academy (13:28:16.030), -' (13:28:26.250), -Welcome (13:28:27.998), -Academy (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Academy (13:29:38.066), -36 (13:30:50.077), -; (13:31:07.806), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -August (13:33:55.549), -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -Weekend (13:37:10.693), -break (13:38:10.544), -; (13:38:10.869)</t>
       </text>
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
@@ -408,7 +408,7 @@
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:35:33.317) ~0.86, -undefined (12:43:17.799) ~0.75, -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -. (13:07:09.027) ~0.00, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.91, -; (13:20:17.407), -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -August (13:33:55.549) ~0.83, -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.62, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967) ~0.88, -Weekend (13:37:10.693) ~0.71, -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +  (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +/ (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Academy (12:35:33.317) ~0.86, -undefined (12:43:17.799) ~0.75, -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -. (13:07:09.027) ~0.00, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.91, -; (13:20:17.407), -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560) ~0.86, -Academy (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Academy (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Academy (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -August (13:33:55.549) ~0.83, -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.62, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967) ~0.88, -Weekend (13:37:10.693) ~0.71, -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +academy (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +academy (00:00:00), +" (00:00:00), +welcome (00:00:00), +academy (00:00:00), +" (00:00:00), +welcome (00:00:00), +  (00:00:00), +academy (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +/ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E41" authorId="0" shapeId="0">
@@ -423,7 +423,7 @@
     </comment>
     <comment ref="J41" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), ++ (00:00:00), +, (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +123456 (00:00:00), +5 (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +&gt; (00:00:00), +Black (00:00:00), +Black (00:00:00), +Boolean (00:00:00), +Brown (00:00:00), +ENter (00:00:00), +JS (00:00:00), +Kaali (00:00:00), +MyBoolean (00:00:00), +Number (00:00:00), +a (00:00:00), +a (00:00:00), +a (00:00:00), +appendchild (00:00:00), +are (00:00:00), +are (00:00:00), +automatically (00:00:00), +characters (00:00:00), +console (00:00:00), +contain (00:00:00), +container (00:00:00), +cript (00:00:00), +document (00:00:00), +for (00:00:00), +getElementById (00:00:00), +global (00:00:00), +ids (00:00:00), +invalid (00:00:00), +javaScript (00:00:00), +lesson (00:00:00), +like (00:00:00), +log (00:00:00), +my (00:00:00), +myArray (00:00:00), +mynumber (00:00:00), +mystring (00:00:00), +names (00:00:00), +names (00:00:00), +need (00:00:00), +no (00:00:00), +numbers (00:00:00), +opposite (00:00:00), +oppositeboolean (00:00:00), +or (00:00:00), +spaces (00:00:00), +special (00:00:00), +start (00:00:00), +string (00:00:00), +that (00:00:00), +valid (00:00:00), +variables (00:00:00), +with (00:00:00), -&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095), -" (13:05:08.847), -black (13:05:20.120), -brown (13:05:24.043), -; (13:07:10.952), -Charlie (13:07:39.223), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -black (13:11:11.856), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+        <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), ++ (00:00:00), +, (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +123456 (00:00:00), +5 (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +&gt; (00:00:00), +Black (00:00:00), +Black (00:00:00), +Boolean (00:00:00), +Brown (00:00:00), +ENter (00:00:00), +JS (00:00:00), +Kaali (00:00:00), +MyBoolean (00:00:00), +Number (00:00:00), +a (00:00:00), +a (00:00:00), +a (00:00:00), +appendchild (00:00:00), +are (00:00:00), +are (00:00:00), +automatically (00:00:00), +characters (00:00:00), +console (00:00:00), +contain (00:00:00), +container (00:00:00), +cript (00:00:00), +document (00:00:00), +for (00:00:00), +getElementById (00:00:00), +global (00:00:00), +ids (00:00:00), +invalid (00:00:00), +javaScript (00:00:00), +lesson (00:00:00), +like (00:00:00), +log (00:00:00), +my (00:00:00), +myArray (00:00:00), +mynumber (00:00:00), +mystring (00:00:00), +names (00:00:00), +names (00:00:00), +need (00:00:00), +no (00:00:00), +numbers (00:00:00), +opposite (00:00:00), +oppositeboolean (00:00:00), +or (00:00:00), +spaces (00:00:00), +special (00:00:00), +start (00:00:00), +string (00:00:00), +that (00:00:00), +valid (00:00:00), +variables (00:00:00), +with (00:00:00), -&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095), -" (13:05:08.847), -black (13:05:20.120), -brown (13:05:24.043), -; (13:07:10.952), -Charlie (13:07:39.223), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -black (13:11:11.856), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Academy (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Academy (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
       </text>
     </comment>
     <comment ref="M41" authorId="0" shapeId="0">
@@ -433,12 +433,12 @@
     </comment>
     <comment ref="O41" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095) ~0.00, -" (13:05:08.847) ~0.00, -black (13:05:20.120) ~0.80, -brown (13:05:24.043) ~0.80, -; (13:07:10.952), -Charlie (13:07:39.223) ~0.43, -black (13:11:11.856) ~0.80, -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095) ~0.00, -" (13:05:08.847) ~0.00, -black (13:05:20.120) ~0.80, -brown (13:05:24.043) ~0.80, -; (13:07:10.952), -Charlie (13:07:39.223) ~0.43, -black (13:11:11.856) ~0.80, -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Academy (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Academy (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
       <text>
-        <t>" (x2), ,, Emnet, First, abbbriviations, anotherdog (x2), karelia (x2), o1 (x3), swtich</t>
+        <t>" (x2), ,, Emnet, First, abbbriviations, anotherdog (x2), academy (x2), o1 (x3), swtich</t>
       </text>
     </comment>
     <comment ref="H42" authorId="0" shapeId="0">
@@ -448,7 +448,7 @@
     </comment>
     <comment ref="J42" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
+        <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +academy (00:00:00), +academy (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Academy (12:35:33.317), -; (12:35:38.458), -Academy (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
       </text>
     </comment>
     <comment ref="M42" authorId="0" shapeId="0">
@@ -458,12 +458,12 @@
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:35:33.317) ~0.86, -; (12:35:38.458), -Karelia (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520) ~0.67, +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
+        <t>-Academy (12:35:33.317) ~0.86, -; (12:35:38.458), -Academy (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520) ~0.67, +academy (00:00:00), +academy (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
       <text>
-        <t>" (x2), ' (x2), Charle, abbreviation, august, friday, getDate, karelia, max, mynumber (x2), orderlist, thursday, tuesday, viewpoint, wednesday, weekend</t>
+        <t>" (x2), ' (x2), Charle, abbreviation, august, friday, getDate, academy, max, mynumber (x2), orderlist, thursday, tuesday, viewpoint, wednesday, weekend</t>
       </text>
     </comment>
     <comment ref="H45" authorId="0" shapeId="0">
@@ -473,7 +473,7 @@
     </comment>
     <comment ref="J45" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +Charle (00:00:00), +abbreviation (00:00:00), +august (00:00:00), +friday (00:00:00), +getDate (00:00:00), +karelia (00:00:00), +max (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +orderlist (00:00:00), +thursday (00:00:00), +tuesday (00:00:00), +viewpoint (00:00:00), +wednesday (00:00:00), +weekend (00:00:00), -viewport (12:24:12.738), -abbreviations (12:29:01.416), -ordered (12:31:02.226), -list (12:31:03.447), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:46:59.354), -Max (13:05:08.613), -Charlie (13:07:39.223), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -getDay (13:34:50.180), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693)</t>
+        <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +Charle (00:00:00), +abbreviation (00:00:00), +august (00:00:00), +friday (00:00:00), +getDate (00:00:00), +academy (00:00:00), +max (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +orderlist (00:00:00), +thursday (00:00:00), +tuesday (00:00:00), +viewpoint (00:00:00), +wednesday (00:00:00), +weekend (00:00:00), -viewport (12:24:12.738), -abbreviations (12:29:01.416), -ordered (12:31:02.226), -list (12:31:03.447), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -Academy (12:46:59.354), -Max (13:05:08.613), -Charlie (13:07:39.223), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -getDay (13:34:50.180), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693)</t>
       </text>
     </comment>
     <comment ref="M45" authorId="0" shapeId="0">
@@ -483,12 +483,12 @@
     </comment>
     <comment ref="O45" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -Charlie (13:07:39.223) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -getDay (13:34:50.180) ~0.71, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.83, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Academy (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -Charlie (13:07:39.223) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -getDay (13:34:50.180) ~0.71, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.83, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +academy (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E46" authorId="0" shapeId="0">
       <text>
-        <t>Furr, Html, Kareliaa, Lession, defult, year, log*</t>
+        <t>Furr, Html, Academya, Lession, defult, year, log*</t>
       </text>
     </comment>
     <comment ref="H46" authorId="0" shapeId="0">
@@ -498,7 +498,7 @@
     </comment>
     <comment ref="J46" authorId="0" shapeId="0">
       <text>
-        <t>+Furr (00:00:00), +Html (00:00:00), +Kareliaa (00:00:00), +Lession (00:00:00), +defult (00:00:00), +year (00:00:00), -Lesson (12:24:25.593), -HTML (12:30:43.236), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818), -default (13:37:00.967)</t>
+        <t>+Furr (00:00:00), +Html (00:00:00), +Academya (00:00:00), +Lession (00:00:00), +defult (00:00:00), +year (00:00:00), -Lesson (12:24:25.593), -HTML (12:30:43.236), -Academy (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818), -default (13:37:00.967)</t>
       </text>
     </comment>
     <comment ref="M46" authorId="0" shapeId="0">
@@ -508,12 +508,12 @@
     </comment>
     <comment ref="O46" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:46:59.354) ~0.88, +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077) ~0.75, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818) ~0.80, -default (13:37:00.967) ~0.86, +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
+        <t>-Academy (12:46:59.354) ~0.88, +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077) ~0.75, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818) ~0.80, -default (13:37:00.967) ~0.86, +Academya (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E48" authorId="0" shapeId="0">
       <text>
-        <t>" (x2), Agust, Karelia, Numbers, Viewport, charlie, comsole, cosole, date (x2), intial, karelia, lesson, order</t>
+        <t>" (x2), Agust, Academy, Numbers, Viewport, charlie, comsole, cosole, date (x2), intial, academy, lesson, order</t>
       </text>
     </comment>
     <comment ref="H48" authorId="0" shapeId="0">
@@ -523,7 +523,7 @@
     </comment>
     <comment ref="J48" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +Agust (00:00:00), +Karelia (00:00:00), +Numbers (00:00:00), +Viewport (00:00:00), +charlie (00:00:00), +comsole (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +intial (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +order (00:00:00), -viewport (12:24:12.738), -initial (12:24:13.118), -Lesson (12:24:25.593), -/ (12:29:39.313), -ordered (12:31:02.226), -Charlie (13:07:39.223), -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678)</t>
+        <t>+" (00:00:00), +" (00:00:00), +Agust (00:00:00), +Academy (00:00:00), +Numbers (00:00:00), +Viewport (00:00:00), +charlie (00:00:00), +comsole (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +intial (00:00:00), +academy (00:00:00), +lesson (00:00:00), +order (00:00:00), -viewport (12:24:12.738), -initial (12:24:13.118), -Lesson (12:24:25.593), -/ (12:29:39.313), -ordered (12:31:02.226), -Charlie (13:07:39.223), -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Academy (13:29:38.066), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678)</t>
       </text>
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
@@ -533,7 +533,7 @@
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
       <text>
-        <t>-Charlie (13:07:39.223) ~0.86, -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066) ~0.86, -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
+        <t>-Charlie (13:07:39.223) ~0.86, -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Academy (13:29:38.066) ~0.86, -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +Academy (00:00:00), +academy (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -573,7 +573,7 @@
     </comment>
     <comment ref="J51" authorId="0" shapeId="0">
       <text>
-        <t>+22 (00:00:00), +Karela (00:00:00), +Lession (00:00:00), +abbreviatios (00:00:00), -Lesson (12:24:25.593), -abbreviations (12:29:01.416), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030), -36 (13:30:50.077)</t>
+        <t>+22 (00:00:00), +Karela (00:00:00), +Lession (00:00:00), +abbreviatios (00:00:00), -Lesson (12:24:25.593), -abbreviations (12:29:01.416), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Academy (13:28:16.030), -36 (13:30:50.077)</t>
       </text>
     </comment>
     <comment ref="M51" authorId="0" shapeId="0">
@@ -583,12 +583,12 @@
     </comment>
     <comment ref="O51" authorId="0" shapeId="0">
       <text>
-        <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030) ~0.86, -36 (13:30:50.077) ~0.00, +Karela (00:00:00), +22 (00:00:00)</t>
+        <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Academy (13:28:16.030) ~0.86, -36 (13:30:50.077) ~0.00, +Karela (00:00:00), +22 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E56" authorId="0" shapeId="0">
       <text>
-        <t>", ' (x2), (, ), , (x4), ., 19, 2006, 28, 4, 5, 55, 67 (x2), ; (x2), =, December, Hello (x2), XXX, Years, a, console, const, containter, item, karelia (x3), log, rex</t>
+        <t>", ' (x2), (, ), , (x4), ., 19, 2006, 28, 4, 5, 55, 67 (x2), ; (x2), =, December, Hello (x2), XXX, Years, a, console, const, containter, item, academy (x3), log, rex</t>
       </text>
     </comment>
     <comment ref="H56" authorId="0" shapeId="0">
@@ -598,7 +598,7 @@
     </comment>
     <comment ref="J56" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +) (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +. (00:00:00), +19 (00:00:00), +2006 (00:00:00), +28 (00:00:00), +4 (00:00:00), +5 (00:00:00), +55 (00:00:00), +67 (00:00:00), +67 (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +December (00:00:00), +Hello (00:00:00), +Hello (00:00:00), +XXX (00:00:00), +Years (00:00:00), +a (00:00:00), +console (00:00:00), +const (00:00:00), +containter (00:00:00), +item (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +log (00:00:00), +rex (00:00:00), -container (12:30:48.969), -items (12:31:06.206), -25 (12:33:49.617), -2 (12:33:50.650), -; (12:36:56.445), -Karelia (12:46:59.354), -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170), -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030), -! (13:28:16.362), -Karelia (13:28:30.418), -! (13:28:30.583), -" (13:29:31.463), -Karelia (13:29:38.066), -36 (13:30:50.077), -years (13:32:12.609), -; (13:32:15.376), -August (13:33:55.549), -24 (13:33:56.247), -2025 (13:33:58.460)</t>
+        <t>+" (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +) (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +. (00:00:00), +19 (00:00:00), +2006 (00:00:00), +28 (00:00:00), +4 (00:00:00), +5 (00:00:00), +55 (00:00:00), +67 (00:00:00), +67 (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +December (00:00:00), +Hello (00:00:00), +Hello (00:00:00), +XXX (00:00:00), +Years (00:00:00), +a (00:00:00), +console (00:00:00), +const (00:00:00), +containter (00:00:00), +item (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +log (00:00:00), +rex (00:00:00), -container (12:30:48.969), -items (12:31:06.206), -25 (12:33:49.617), -2 (12:33:50.650), -; (12:36:56.445), -Academy (12:46:59.354), -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170), -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Academy (13:28:16.030), -! (13:28:16.362), -Academy (13:28:30.418), -! (13:28:30.583), -" (13:29:31.463), -Academy (13:29:38.066), -36 (13:30:50.077), -years (13:32:12.609), -; (13:32:15.376), -August (13:33:55.549), -24 (13:33:56.247), -2025 (13:33:58.460)</t>
       </text>
     </comment>
     <comment ref="M56" authorId="0" shapeId="0">
@@ -608,12 +608,12 @@
     </comment>
     <comment ref="O56" authorId="0" shapeId="0">
       <text>
-        <t>-25 (12:33:49.617) ~0.00, -2 (12:33:50.650) ~0.00, -; (12:36:56.445), -Karelia (12:46:59.354) ~0.00, -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170) ~0.67, -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -" (13:29:31.463) ~0.00, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:32:12.609) ~0.80, -; (13:32:15.376), -August (13:33:55.549) ~0.00, -24 (13:33:56.247) ~0.50, -2025 (13:33:58.460) ~0.50, +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
+        <t>-25 (12:33:49.617) ~0.00, -2 (12:33:50.650) ~0.00, -; (12:36:56.445), -Academy (12:46:59.354) ~0.00, -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170) ~0.67, -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Academy (13:28:16.030) ~0.86, -! (13:28:16.362), -Academy (13:28:30.418) ~0.86, -! (13:28:30.583), -" (13:29:31.463) ~0.00, -Academy (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:32:12.609) ~0.80, -; (13:32:15.376), -August (13:33:55.549) ~0.00, -24 (13:33:56.247) ~0.50, -2025 (13:33:58.460) ~0.50, +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +academy (00:00:00), +academy (00:00:00), +' (00:00:00), +academy (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E59" authorId="0" shapeId="0">
       <text>
-        <t>" (x2), 1 (x4), Console, SomeDate, abbreviation, karelia, toady</t>
+        <t>" (x2), 1 (x4), Console, SomeDate, abbreviation, academy, toady</t>
       </text>
     </comment>
     <comment ref="H59" authorId="0" shapeId="0">
@@ -623,7 +623,7 @@
     </comment>
     <comment ref="J59" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +Console (00:00:00), +SomeDate (00:00:00), +abbreviation (00:00:00), +karelia (00:00:00), +toady (00:00:00), -abbreviations (12:29:01.416), -Karelia (12:46:59.354), -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097)</t>
+        <t>+" (00:00:00), +" (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +Console (00:00:00), +SomeDate (00:00:00), +abbreviation (00:00:00), +academy (00:00:00), +toady (00:00:00), -abbreviations (12:29:01.416), -Academy (12:46:59.354), -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097)</t>
       </text>
     </comment>
     <comment ref="M59" authorId="0" shapeId="0">
@@ -633,7 +633,7 @@
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:46:59.354) ~0.86, -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +karelia (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
+        <t>-Academy (12:46:59.354) ~0.86, -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +academy (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D61" authorId="0" shapeId="0">
@@ -643,7 +643,7 @@
     </comment>
     <comment ref="E61" authorId="0" shapeId="0">
       <text>
-        <t>" (x2), ( (x2), ) (x2), ,, . (x2), 142, ; (x2), Console, First, Math, Ordered, a, appendchild, b, connstmyString, consloe, console, java, karelia (x4), lesson, log, max, mynumber (x2), pow, script, tab, year</t>
+        <t>" (x2), ( (x2), ) (x2), ,, . (x2), 142, ; (x2), Console, First, Math, Ordered, a, appendchild, b, connstmyString, consloe, console, java, academy (x4), lesson, log, max, mynumber (x2), pow, script, tab, year</t>
       </text>
     </comment>
     <comment ref="H61" authorId="0" shapeId="0">
@@ -653,7 +653,7 @@
     </comment>
     <comment ref="J61" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +. (00:00:00), +. (00:00:00), +142 (00:00:00), +; (00:00:00), +; (00:00:00), +Console (00:00:00), +First (00:00:00), +Math (00:00:00), +Ordered (00:00:00), +a (00:00:00), +appendchild (00:00:00), +b (00:00:00), +connstmyString (00:00:00), +consloe (00:00:00), +console (00:00:00), +java (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +log (00:00:00), +max (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +pow (00:00:00), +script (00:00:00), +tab (00:00:00), +year (00:00:00), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -first (12:28:57.481), -! (12:30:40.873), -ordered (12:31:02.226), -Tab (12:31:12.499), -myNumber (12:33:44.402), -console (12:33:56.141), -myNumber (12:33:59.949), -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317), -! (12:42:04.755), -42 (12:42:11.528), -console (12:43:10.202), -Karelia (12:46:59.354), -Max (13:05:08.613), -appendChild (13:13:30.342), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -Karelia (13:29:38.066), -years (13:32:12.609), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+        <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +. (00:00:00), +. (00:00:00), +142 (00:00:00), +; (00:00:00), +; (00:00:00), +Console (00:00:00), +First (00:00:00), +Math (00:00:00), +Ordered (00:00:00), +a (00:00:00), +appendchild (00:00:00), +b (00:00:00), +connstmyString (00:00:00), +consloe (00:00:00), +console (00:00:00), +java (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +lesson (00:00:00), +log (00:00:00), +max (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +pow (00:00:00), +script (00:00:00), +tab (00:00:00), +year (00:00:00), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -first (12:28:57.481), -! (12:30:40.873), -ordered (12:31:02.226), -Tab (12:31:12.499), -myNumber (12:33:44.402), -console (12:33:56.141), -myNumber (12:33:59.949), -const (12:35:25.644), -myString (12:35:27.676), -Academy (12:35:33.317), -! (12:42:04.755), -42 (12:42:11.528), -console (12:43:10.202), -Academy (12:46:59.354), -Max (13:05:08.613), -appendChild (13:13:30.342), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250), -Academy (13:28:30.418), -' (13:28:30.981), -Academy (13:29:38.066), -years (13:32:12.609), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
       </text>
     </comment>
     <comment ref="M61" authorId="0" shapeId="0">
@@ -663,7 +663,7 @@
     </comment>
     <comment ref="O61" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402) ~0.88, -console (12:33:56.141) ~0.71, -myNumber (12:33:59.949) ~0.88, -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317) ~0.86, -! (12:42:04.755), -42 (12:42:11.528) ~0.67, -console (12:43:10.202) ~0.86, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -appendChild (13:13:30.342) ~0.91, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -Karelia (13:29:38.066) ~0.86, -years (13:32:12.609) ~0.80, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00), +; (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -console (12:33:56.141) ~0.71, -myNumber (12:33:59.949) ~0.88, -const (12:35:25.644), -myString (12:35:27.676), -Academy (12:35:33.317) ~0.86, -! (12:42:04.755), -42 (12:42:11.528) ~0.67, -console (12:43:10.202) ~0.86, -Academy (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -appendChild (13:13:30.342) ~0.91, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250) ~0.00, -Academy (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -Academy (13:29:38.066) ~0.86, -years (13:32:12.609) ~0.80, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +academy (00:00:00), +142 (00:00:00), +Console (00:00:00), +academy (00:00:00), +max (00:00:00), +appendchild (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +" (00:00:00), +academy (00:00:00), +" (00:00:00), +academy (00:00:00), +year (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
@@ -723,7 +723,7 @@
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
       <text>
-        <t>" (x3), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, karelia, max, muBoolean, my, orderd, t (x3), title, we, welcome (x3), Document*, log*</t>
+        <t>" (x3), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, academy, max, muBoolean, my, orderd, t (x3), title, we, welcome (x3), Document*, log*</t>
       </text>
     </comment>
     <comment ref="H68" authorId="0" shapeId="0">
@@ -733,7 +733,7 @@
     </comment>
     <comment ref="J68" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +karelia (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
+        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +academy (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Academy (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
       </text>
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
@@ -743,12 +743,12 @@
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Karelia (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -to (13:29:35.300) ~0.50, -" (13:29:36.010), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970) ~0.00, -Wednesday (13:36:38.686) ~0.11, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
+        <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Academy (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -to (13:29:35.300) ~0.50, -" (13:29:36.010), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970) ~0.00, -Wednesday (13:36:38.686) ~0.11, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +academy (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
       <text>
-        <t>", , (x2), / (x3), 22, Console, MAX, aage, anoherDog, karelia (x2), lesson, muBoolean, muNumber, weelend, } (x5), ´ (x2)</t>
+        <t>", , (x2), / (x3), 22, Console, MAX, aage, anoherDog, academy (x2), lesson, muBoolean, muNumber, weelend, } (x5), ´ (x2)</t>
       </text>
     </comment>
     <comment ref="H70" authorId="0" shapeId="0">
@@ -758,7 +758,7 @@
     </comment>
     <comment ref="J70" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +, (00:00:00), +, (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +22 (00:00:00), +Console (00:00:00), +MAX (00:00:00), +aage (00:00:00), +anoherDog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +muBoolean (00:00:00), +muNumber (00:00:00), +weelend (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +´ (00:00:00), +´ (00:00:00), -Lesson (12:24:25.593), -! (12:30:40.873), -myNumber (12:33:44.402), -myBoolean (12:36:27.967), -Karelia (12:46:59.354), -. (12:58:07.899), -; (13:02:35.373), -Max (13:05:08.613), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -age (13:30:48.674), -36 (13:30:50.077), -` (13:32:14.220), -; (13:32:15.376), -console (13:34:46.231), -} (13:35:58.376), -Weekend (13:37:10.693), -; (13:38:10.869)</t>
+        <t>+" (00:00:00), +, (00:00:00), +, (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +22 (00:00:00), +Console (00:00:00), +MAX (00:00:00), +aage (00:00:00), +anoherDog (00:00:00), +academy (00:00:00), +academy (00:00:00), +lesson (00:00:00), +muBoolean (00:00:00), +muNumber (00:00:00), +weelend (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +´ (00:00:00), +´ (00:00:00), -Lesson (12:24:25.593), -! (12:30:40.873), -myNumber (12:33:44.402), -myBoolean (12:36:27.967), -Academy (12:46:59.354), -. (12:58:07.899), -; (13:02:35.373), -Max (13:05:08.613), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -Academy (13:29:38.066), -\ (13:29:38.349), -age (13:30:48.674), -36 (13:30:50.077), -` (13:32:14.220), -; (13:32:15.376), -console (13:34:46.231), -} (13:35:58.376), -Weekend (13:37:10.693), -; (13:38:10.869)</t>
       </text>
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
@@ -768,7 +768,7 @@
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -Karelia (12:46:59.354) ~0.86, -. (12:58:07.899) ~0.00, -; (13:02:35.373) ~0.00, -Max (13:05:08.613) ~0.33, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010), -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -36 (13:30:50.077) ~0.00, -` (13:32:14.220) ~0.00, -; (13:32:15.376), -console (13:34:46.231) ~0.86, -} (13:35:58.376), -Weekend (13:37:10.693) ~0.71, -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -Academy (12:46:59.354) ~0.86, -. (12:58:07.899) ~0.00, -; (13:02:35.373) ~0.00, -Max (13:05:08.613) ~0.33, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010), -Academy (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -36 (13:30:50.077) ~0.00, -` (13:32:14.220) ~0.00, -; (13:32:15.376), -console (13:34:46.231) ~0.86, -} (13:35:58.376), -Weekend (13:37:10.693) ~0.71, -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +academy (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +academy (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H71" authorId="0" shapeId="0">
@@ -788,7 +788,7 @@
     </comment>
     <comment ref="E72" authorId="0" shapeId="0">
       <text>
-        <t>22, Karelia, karelia, studt, todat, viewpoint, year</t>
+        <t>22, Academy, academy, studt, todat, viewpoint, year</t>
       </text>
     </comment>
     <comment ref="H72" authorId="0" shapeId="0">
@@ -798,7 +798,7 @@
     </comment>
     <comment ref="J72" authorId="0" shapeId="0">
       <text>
-        <t>+22 (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +studt (00:00:00), +todat (00:00:00), +viewpoint (00:00:00), +year (00:00:00), -viewport (12:24:12.738), -study (12:35:31.258), -Karelia (12:35:33.317), -36 (13:30:50.077), -years (13:31:05.818), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+        <t>+22 (00:00:00), +Academy (00:00:00), +academy (00:00:00), +studt (00:00:00), +todat (00:00:00), +viewpoint (00:00:00), +year (00:00:00), -viewport (12:24:12.738), -study (12:35:31.258), -Academy (12:35:33.317), -36 (13:30:50.077), -years (13:31:05.818), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
       </text>
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
@@ -808,7 +808,7 @@
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
       <text>
-        <t>-study (12:35:31.258) ~0.80, -Karelia (12:35:33.317) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:31:05.818) ~0.80, -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
+        <t>-study (12:35:31.258) ~0.80, -Academy (12:35:33.317) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:31:05.818) ~0.80, -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +academy (00:00:00), +Academy (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E73" authorId="0" shapeId="0">
@@ -838,7 +838,7 @@
     </comment>
     <comment ref="E75" authorId="0" shapeId="0">
       <text>
-        <t>", / (x2), ;, Boolean (x2), HTMl, browen, charlie, friday, getday, karelia (x5), let, math (x3), max, monday, my, myboolean (x2), myboolen, myoolean, mystring (x2), number, oppositeboolean, port, saturday, tab, thursday, today, tuesday, underfined, view, yeasrs, log*</t>
+        <t>", / (x2), ;, Boolean (x2), HTMl, browen, charlie, friday, getday, academy (x5), let, math (x3), max, monday, my, myboolean (x2), myboolen, myoolean, mystring (x2), number, oppositeboolean, port, saturday, tab, thursday, today, tuesday, underfined, view, yeasrs, log*</t>
       </text>
     </comment>
     <comment ref="H75" authorId="0" shapeId="0">
@@ -848,7 +848,7 @@
     </comment>
     <comment ref="J75" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +HTMl (00:00:00), +browen (00:00:00), +charlie (00:00:00), +friday (00:00:00), +getday (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +saturday (00:00:00), +tab (00:00:00), +thursday (00:00:00), +today (00:00:00), +tuesday (00:00:00), +underfined (00:00:00), +view (00:00:00), +yeasrs (00:00:00), -viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), -myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
+        <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +HTMl (00:00:00), +browen (00:00:00), +charlie (00:00:00), +friday (00:00:00), +getday (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +saturday (00:00:00), +tab (00:00:00), +thursday (00:00:00), +today (00:00:00), +tuesday (00:00:00), +underfined (00:00:00), +view (00:00:00), +yeasrs (00:00:00), -viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), -myString (12:35:27.676), -Academy (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Academy (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Academy (13:28:16.030), -' (13:28:26.250), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759), -Academy (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
       </text>
     </comment>
     <comment ref="M75" authorId="0" shapeId="0">
@@ -858,7 +858,7 @@
     </comment>
     <comment ref="O75" authorId="0" shapeId="0">
       <text>
-        <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108), -myBoolean (12:41:00.416) ~0.89, -; (12:41:04.494), -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, -Karelia (12:46:59.354) ~0.86, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613) ~0.67, -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -; (13:26:07.158), -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759) ~0.00, -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -years (13:32:12.609) ~0.83, -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019) ~0.25, -getDay (13:35:54.315) ~0.83, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.44, -Thursday (13:36:45.577) ~0.50, -Friday (13:36:53.097) ~0.38, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +today (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
+        <t>-myString (12:35:27.676) ~0.88, -Academy (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108), -myBoolean (12:41:00.416) ~0.89, -; (12:41:04.494), -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, -Academy (12:46:59.354) ~0.86, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613) ~0.67, -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -; (13:26:07.158), -Academy (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Academy (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759) ~0.00, -Academy (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -years (13:32:12.609) ~0.83, -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019) ~0.25, -getDay (13:35:54.315) ~0.83, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.44, -Thursday (13:36:45.577) ~0.50, -Friday (13:36:53.097) ~0.38, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +mystring (00:00:00), +academy (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +academy (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +academy (00:00:00), +" (00:00:00), +academy (00:00:00), +/ (00:00:00), +academy (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +today (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -943,12 +943,12 @@
     </comment>
     <comment ref="J82" authorId="0" shapeId="0">
       <text>
-        <t>+21 (00:00:00), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), -ABC (12:42:20.731), -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354), -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077), -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077), -; (13:31:07.806), -; (13:32:15.376)</t>
+        <t>+21 (00:00:00), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), -ABC (12:42:20.731), -; (12:42:36.696), -; (12:43:22.016), -Academy (12:46:59.354), -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077), -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077), -; (13:31:07.806), -; (13:32:15.376)</t>
       </text>
     </comment>
     <comment ref="O82" authorId="0" shapeId="0">
       <text>
-        <t>-ABC (12:42:20.731) ~0.00, -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354) ~0.00, -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077) ~0.75, -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
+        <t>-ABC (12:42:20.731) ~0.00, -; (12:42:36.696), -; (12:43:22.016), -Academy (12:46:59.354) ~0.00, -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077) ~0.75, -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E83" authorId="0" shapeId="0">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>" (x4), 22, Agust, KArelia, Wwlcome, anotherdog, braeak, charlie, coneole, const, friday, karelia (x4), pold, tab, wednesday, }</t>
+          <t>" (x4), 22, Agust, ACademy, Wwlcome, anotherdog, braeak, charlie, coneole, const, friday, academy (x4), pold, tab, wednesday, }</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +22 (00:00:00), +Agust (00:00:00), +KArelia (00:00:00), +Wwlcome (00:00:00), +anotherdog (00:00:00), +braeak (00:00:00), +charlie (00:00:00), +coneole (00:00:00), +const (00:00:00), +friday (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +pold (00:00:00), +tab (00:00:00), +wednesday (00:00:00), +} (00:00:00), -Tab (12:31:12.499), -Karelia (12:35:33.317), -Karelia (12:46:59.354), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066), -36 (13:30:50.077), -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881), -` (13:31:57.168), -` (13:32:14.220), -; (13:33:31.713), -August (13:33:55.549), -Wednesday (13:36:38.686), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736)</t>
+          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +22 (00:00:00), +Agust (00:00:00), +ACademy (00:00:00), +Wwlcome (00:00:00), +anotherdog (00:00:00), +braeak (00:00:00), +charlie (00:00:00), +coneole (00:00:00), +const (00:00:00), +friday (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +pold (00:00:00), +tab (00:00:00), +wednesday (00:00:00), +} (00:00:00), -Tab (12:31:12.499), -Academy (12:35:33.317), -Academy (12:46:59.354), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -Welcome (13:28:13.560), -Academy (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Academy (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Academy (13:29:38.066), -36 (13:30:50.077), -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881), -` (13:31:57.168), -` (13:32:14.220), -; (13:33:31.713), -August (13:33:55.549), -Wednesday (13:36:38.686), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736)</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.90, -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881) ~0.75, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -; (13:33:31.713), -August (13:33:55.549) ~0.83, -Wednesday (13:36:38.686) ~0.89, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736) ~0.83, +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
+          <t>-Academy (12:35:33.317) ~0.86, -Academy (12:46:59.354) ~0.86, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.90, -; (13:20:09.716), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -Welcome (13:28:13.560) ~0.86, -Academy (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Academy (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Academy (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881) ~0.75, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -; (13:33:31.713), -August (13:33:55.549) ~0.83, -Wednesday (13:36:38.686) ~0.89, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736) ~0.83, +const (00:00:00), +academy (00:00:00), +academy (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +ACademy (00:00:00), +" (00:00:00), +academy (00:00:00), +" (00:00:00), +academy (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Javascript, karelia (x4), mystring (x2), welcome</t>
+          <t>Javascript, academy (x4), mystring (x2), welcome</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+Javascript (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +welcome (00:00:00), -JavaScript (12:24:24.306), -myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -Karelia (12:46:59.354), -Karelia (13:28:16.030), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -` (13:31:57.168), -` (13:32:14.220)</t>
+          <t>+Javascript (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +welcome (00:00:00), -JavaScript (12:24:24.306), -myString (12:35:27.676), -Academy (12:35:33.317), -myString (12:35:43.276), -Academy (12:46:59.354), -Academy (13:28:16.030), -Welcome (13:28:27.998), -Academy (13:28:30.418), -` (13:31:57.168), -` (13:32:14.220)</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -Karelia (12:46:59.354) ~0.86, -Karelia (13:28:16.030) ~0.86, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
+          <t>-myString (12:35:27.676) ~0.88, -Academy (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -Academy (12:46:59.354) ~0.86, -Academy (13:28:16.030) ~0.86, -Welcome (13:28:27.998) ~0.86, -Academy (13:28:30.418) ~0.86, -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +academy (00:00:00), +mystring (00:00:00), +academy (00:00:00), +academy (00:00:00), +welcome (00:00:00), +academy (00:00:00)</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> , ", , (x2), 1, 2, 3, ;, =, Agust, [, ], abbreaviations, date, karelia, max, myArray, welcome</t>
+          <t xml:space="preserve"> , ", , (x2), 1, 2, 3, ;, =, Agust, [, ], abbreaviations, date, academy, max, myArray, welcome</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+  (00:00:00), +" (00:00:00), +, (00:00:00), +, (00:00:00), +1 (00:00:00), +2 (00:00:00), +3 (00:00:00), +; (00:00:00), += (00:00:00), +Agust (00:00:00), +[ (00:00:00), +] (00:00:00), +abbreaviations (00:00:00), +date (00:00:00), +karelia (00:00:00), +max (00:00:00), +myArray (00:00:00), +welcome (00:00:00), -abbreviations (12:29:01.416), -Karelia (12:35:33.317), -Max (13:05:08.613), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560), -Date (13:33:53.451), -August (13:33:55.549)</t>
+          <t>+  (00:00:00), +" (00:00:00), +, (00:00:00), +, (00:00:00), +1 (00:00:00), +2 (00:00:00), +3 (00:00:00), +; (00:00:00), += (00:00:00), +Agust (00:00:00), +[ (00:00:00), +] (00:00:00), +abbreaviations (00:00:00), +date (00:00:00), +academy (00:00:00), +max (00:00:00), +myArray (00:00:00), +welcome (00:00:00), -abbreviations (12:29:01.416), -Academy (12:35:33.317), -Max (13:05:08.613), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560), -Date (13:33:53.451), -August (13:33:55.549)</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-Karelia (12:35:33.317) ~0.86, -Max (13:05:08.613) ~0.67, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560) ~0.86, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
+          <t>-Academy (12:35:33.317) ~0.86, -Max (13:05:08.613) ~0.67, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Welcome (13:28:13.560) ~0.86, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +academy (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +- (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +03 (00:00:00), +10 (00:00:00), +2024 (00:00:00), +6 (00:00:00), +7 (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +Charley (00:00:00), +Friday (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +Saturday (00:00:00), +Thursday (00:00:00), +Wednesday (00:00:00), +` (00:00:00), +` (00:00:00), +am (00:00:00), +break (00:00:00), +break (00:00:00), +case (00:00:00), +case (00:00:00), +console (00:00:00), +console (00:00:00), +eys (00:00:00), +folowed (00:00:00), +log (00:00:00), +log (00:00:00), +max (00:00:00), +monday (00:00:00), +myBoolean (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +someDay (00:00:00), +someDay (00:00:00), +studing (00:00:00), +tusday (00:00:00), +weekend (00:00:00), -: (12:29:02.589), -followed (12:31:10.973), -study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095), -Max (13:05:08.613), -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524), -" (13:05:23.089), -" (13:05:24.754), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -" (13:07:52.850), -" (13:07:53.974), -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437), -" (13:20:07.578), -" (13:20:08.157), -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026)</t>
+          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +- (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +03 (00:00:00), +10 (00:00:00), +2024 (00:00:00), +6 (00:00:00), +7 (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +Charley (00:00:00), +Friday (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +It (00:00:00), +Saturday (00:00:00), +Thursday (00:00:00), +Wednesday (00:00:00), +` (00:00:00), +` (00:00:00), +am (00:00:00), +break (00:00:00), +break (00:00:00), +case (00:00:00), +case (00:00:00), +console (00:00:00), +console (00:00:00), +eys (00:00:00), +folowed (00:00:00), +log (00:00:00), +log (00:00:00), +max (00:00:00), +monday (00:00:00), +myBoolean (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +s (00:00:00), +someDay (00:00:00), +someDay (00:00:00), +studing (00:00:00), +tusday (00:00:00), +weekend (00:00:00), -: (12:29:02.589), -followed (12:31:10.973), -study (12:35:31.258), -at (12:35:31.858), -Academy (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095), -Max (13:05:08.613), -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524), -" (13:05:23.089), -" (13:05:24.754), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -" (13:07:52.850), -" (13:07:53.974), -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437), -" (13:20:07.578), -" (13:20:08.157), -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026)</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095) ~0.00, -Max (13:05:08.613) ~0.67, -" (13:05:08.847) ~0.00, -" (13:05:18.869) ~0.00, -" (13:05:20.541) ~0.00, -eyes (13:05:22.524) ~0.75, -" (13:05:23.089) ~0.00, -" (13:05:24.754) ~0.00, -" (13:07:37.700) ~0.00, -Charlie (13:07:39.223) ~0.71, -" (13:07:39.689) ~0.00, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -" (13:10:58.977) ~0.00, -" (13:11:00.402) ~0.00, -" (13:11:05.379) ~0.00, -" (13:11:09.329) ~0.00, -" (13:11:10.342) ~0.00, -" (13:11:12.437) ~0.00, -" (13:20:07.578) ~0.00, -" (13:20:08.157) ~0.00, -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463) ~0.00, -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019) ~0.75, -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667) ~0.75, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.71, -Thursday (13:36:45.577) ~0.44, -Friday (13:36:53.097) ~0.50, -Weekend (13:37:10.693) ~0.86, -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +, (00:00:00), +myBoolean (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
+          <t>-study (12:35:31.258), -at (12:35:31.858), -Academy (12:35:33.317), -myBoolean (12:38:28.108), -, (12:38:28.542), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -; (13:05:06.814), -" (13:05:08.095) ~0.00, -Max (13:05:08.613) ~0.67, -" (13:05:08.847) ~0.00, -" (13:05:18.869) ~0.00, -" (13:05:20.541) ~0.00, -eyes (13:05:22.524) ~0.75, -" (13:05:23.089) ~0.00, -" (13:05:24.754) ~0.00, -" (13:07:37.700) ~0.00, -Charlie (13:07:39.223) ~0.71, -" (13:07:39.689) ~0.00, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -" (13:10:58.977) ~0.00, -" (13:11:00.402) ~0.00, -" (13:11:05.379) ~0.00, -" (13:11:09.329) ~0.00, -" (13:11:10.342) ~0.00, -" (13:11:12.437) ~0.00, -" (13:20:07.578) ~0.00, -" (13:20:08.157) ~0.00, -; (13:22:53.102), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463) ~0.00, -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -someDate (13:33:51.019) ~0.75, -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667) ~0.75, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.71, -Thursday (13:36:45.577) ~0.44, -Friday (13:36:53.097) ~0.50, -Weekend (13:37:10.693) ~0.86, -; (13:38:10.869), -; (13:38:13.634), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +, (00:00:00), +myBoolean (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
       <c r="Q21" s="4" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>" (x2), ' (x2), +, , (x2), 3, Container, Dog (x6), Id, august, charlie, cosole, emmet, enter, fraiday, html, i (x2), in, javascript, karelia (x5), lesson, math (x3), max, monday, my, mynumber (x2), rex, tab, thursday, tuesday, weekend, welcome (x3), wendsday</t>
+          <t>" (x2), ' (x2), +, , (x2), 3, Container, Dog (x6), Id, august, charlie, cosole, emmet, enter, fraiday, html, i (x2), in, javascript, academy (x5), lesson, math (x3), max, monday, my, mynumber (x2), rex, tab, thursday, tuesday, weekend, welcome (x3), wendsday</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), ++ (00:00:00), +, (00:00:00), +, (00:00:00), +3 (00:00:00), +Container (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Id (00:00:00), +august (00:00:00), +charlie (00:00:00), +cosole (00:00:00), +emmet (00:00:00), +enter (00:00:00), +fraiday (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +javascript (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +rex (00:00:00), +tab (00:00:00), +thursday (00:00:00), +tuesday (00:00:00), +weekend (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +wendsday (00:00:00), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -id (12:27:55.052), -My (12:28:56.380), -Emmet (12:28:58.636), -HTML (12:30:43.236), -Tab (12:31:12.499), -Enter (12:31:14.293), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -at (12:35:31.858), -Karelia (12:35:33.317), -Karelia (12:46:59.354), -2 (12:48:52.350), -dog (13:05:03.658), -Max (13:05:08.613), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -Charlie (13:07:39.223), -dog (13:07:52.399), -Rex (13:11:00.170), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -I (13:30:59.741), -` (13:31:57.168), -I (13:32:08.777), -` (13:32:14.220), -August (13:33:55.549), -console (13:34:01.942), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693)</t>
+          <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), ++ (00:00:00), +, (00:00:00), +, (00:00:00), +3 (00:00:00), +Container (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Id (00:00:00), +august (00:00:00), +charlie (00:00:00), +cosole (00:00:00), +emmet (00:00:00), +enter (00:00:00), +fraiday (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +javascript (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +lesson (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +rex (00:00:00), +tab (00:00:00), +thursday (00:00:00), +tuesday (00:00:00), +weekend (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +wendsday (00:00:00), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -id (12:27:55.052), -My (12:28:56.380), -Emmet (12:28:58.636), -HTML (12:30:43.236), -Tab (12:31:12.499), -Enter (12:31:14.293), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -at (12:35:31.858), -Academy (12:35:33.317), -Academy (12:46:59.354), -2 (12:48:52.350), -dog (13:05:03.658), -Max (13:05:08.613), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -Charlie (13:07:39.223), -dog (13:07:52.399), -Rex (13:11:00.170), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -Welcome (13:28:13.560), -Academy (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Academy (13:29:38.066), -I (13:30:59.741), -` (13:31:57.168), -I (13:32:08.777), -` (13:32:14.220), -August (13:33:55.549), -console (13:34:01.942), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693)</t>
         </is>
       </c>
       <c r="M25" t="n">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -at (12:35:31.858) ~0.00, -Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -2 (12:48:52.350) ~0.00, -dog (13:05:03.658) ~0.67, -Max (13:05:08.613) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -dog (13:07:52.399) ~0.67, -Rex (13:11:00.170) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -I (13:30:59.741) ~0.00, -` (13:31:57.168) ~0.00, -I (13:32:08.777) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -console (13:34:01.942) ~0.86, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.67, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.71, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -at (12:35:31.858) ~0.00, -Academy (12:35:33.317) ~0.86, -Academy (12:46:59.354) ~0.86, -2 (12:48:52.350) ~0.00, -dog (13:05:03.658) ~0.67, -Max (13:05:08.613) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -dog (13:07:52.399) ~0.67, -Rex (13:11:00.170) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -Welcome (13:28:13.560) ~0.86, -Academy (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Academy (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Academy (13:29:38.066) ~0.86, -I (13:30:59.741) ~0.00, -` (13:31:57.168) ~0.00, -I (13:32:08.777) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -console (13:34:01.942) ~0.86, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.67, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.71, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +academy (00:00:00), +, (00:00:00), +academy (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +academy (00:00:00), +" (00:00:00), +welcome (00:00:00), +academy (00:00:00), +" (00:00:00), +welcome (00:00:00), +academy (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> , " (x2), ' (x2), , (x4), -, /, 21, Javascript, anpotherDog, august, charlie, defeault, friday, html, karelia (x4), lesson, max, monday, mynumber (x2), powb, someData, tab, thrusday, tuesday, underdefined, utf, wednesday, weekwnd, welcome (x3), log*</t>
+          <t xml:space="preserve"> , " (x2), ' (x2), , (x4), -, /, 21, Javascript, anpotherDog, august, charlie, defeault, friday, html, academy (x4), lesson, max, monday, mynumber (x2), powb, someData, tab, thrusday, tuesday, underdefined, utf, wednesday, weekwnd, welcome (x3), log*</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +/ (00:00:00), +21 (00:00:00), +Javascript (00:00:00), +anpotherDog (00:00:00), +august (00:00:00), +charlie (00:00:00), +defeault (00:00:00), +friday (00:00:00), +html (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +max (00:00:00), +monday (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +powb (00:00:00), +someData (00:00:00), +tab (00:00:00), +thrusday (00:00:00), +tuesday (00:00:00), +underdefined (00:00:00), +utf (00:00:00), +wednesday (00:00:00), +weekwnd (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), -! (12:24:11.928), -UTF (12:24:12.488), -= (12:24:13.188), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -/ (12:29:39.313), -Tab (12:31:12.499), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:35:33.317), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -. (13:07:09.027), -Charlie (13:07:39.223), -https (13:09:28.845), -anotherDog (13:10:55.220), -; (13:20:17.407), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -36 (13:30:50.077), -; (13:31:07.806), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -August (13:33:55.549), -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -Weekend (13:37:10.693), -break (13:38:10.544), -; (13:38:10.869)</t>
+          <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +/ (00:00:00), +21 (00:00:00), +Javascript (00:00:00), +anpotherDog (00:00:00), +august (00:00:00), +charlie (00:00:00), +defeault (00:00:00), +friday (00:00:00), +html (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +lesson (00:00:00), +max (00:00:00), +monday (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +powb (00:00:00), +someData (00:00:00), +tab (00:00:00), +thrusday (00:00:00), +tuesday (00:00:00), +underdefined (00:00:00), +utf (00:00:00), +wednesday (00:00:00), +weekwnd (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), -! (12:24:11.928), -UTF (12:24:12.488), -= (12:24:13.188), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -/ (12:29:39.313), -Tab (12:31:12.499), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -Academy (12:35:33.317), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -. (13:07:09.027), -Charlie (13:07:39.223), -https (13:09:28.845), -anotherDog (13:10:55.220), -; (13:20:17.407), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560), -Academy (13:28:16.030), -' (13:28:26.250), -Welcome (13:28:27.998), -Academy (13:28:30.418), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -Academy (13:29:38.066), -36 (13:30:50.077), -; (13:31:07.806), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -August (13:33:55.549), -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -Weekend (13:37:10.693), -break (13:38:10.544), -; (13:38:10.869)</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:35:33.317) ~0.86, -undefined (12:43:17.799) ~0.75, -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -. (13:07:09.027) ~0.00, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.91, -; (13:20:17.407), -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -August (13:33:55.549) ~0.83, -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.62, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967) ~0.88, -Weekend (13:37:10.693) ~0.71, -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +  (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +/ (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Academy (12:35:33.317) ~0.86, -undefined (12:43:17.799) ~0.75, -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -. (13:07:09.027) ~0.00, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.91, -; (13:20:17.407), -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560) ~0.86, -Academy (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -Academy (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -Academy (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -August (13:33:55.549) ~0.83, -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.62, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967) ~0.88, -Weekend (13:37:10.693) ~0.71, -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +academy (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +academy (00:00:00), +" (00:00:00), +welcome (00:00:00), +academy (00:00:00), +" (00:00:00), +welcome (00:00:00), +  (00:00:00), +academy (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +/ (00:00:00)</t>
         </is>
       </c>
       <c r="Q36" s="4" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), ++ (00:00:00), +, (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +123456 (00:00:00), +5 (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +&gt; (00:00:00), +Black (00:00:00), +Black (00:00:00), +Boolean (00:00:00), +Brown (00:00:00), +ENter (00:00:00), +JS (00:00:00), +Kaali (00:00:00), +MyBoolean (00:00:00), +Number (00:00:00), +a (00:00:00), +a (00:00:00), +a (00:00:00), +appendchild (00:00:00), +are (00:00:00), +are (00:00:00), +automatically (00:00:00), +characters (00:00:00), +console (00:00:00), +contain (00:00:00), +container (00:00:00), +cript (00:00:00), +document (00:00:00), +for (00:00:00), +getElementById (00:00:00), +global (00:00:00), +ids (00:00:00), +invalid (00:00:00), +javaScript (00:00:00), +lesson (00:00:00), +like (00:00:00), +log (00:00:00), +my (00:00:00), +myArray (00:00:00), +mynumber (00:00:00), +mystring (00:00:00), +names (00:00:00), +names (00:00:00), +need (00:00:00), +no (00:00:00), +numbers (00:00:00), +opposite (00:00:00), +oppositeboolean (00:00:00), +or (00:00:00), +spaces (00:00:00), +special (00:00:00), +start (00:00:00), +string (00:00:00), +that (00:00:00), +valid (00:00:00), +variables (00:00:00), +with (00:00:00), -&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095), -" (13:05:08.847), -black (13:05:20.120), -brown (13:05:24.043), -; (13:07:10.952), -Charlie (13:07:39.223), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -black (13:11:11.856), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+          <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), ++ (00:00:00), +, (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +123456 (00:00:00), +5 (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +&gt; (00:00:00), +Black (00:00:00), +Black (00:00:00), +Boolean (00:00:00), +Brown (00:00:00), +ENter (00:00:00), +JS (00:00:00), +Kaali (00:00:00), +MyBoolean (00:00:00), +Number (00:00:00), +a (00:00:00), +a (00:00:00), +a (00:00:00), +appendchild (00:00:00), +are (00:00:00), +are (00:00:00), +automatically (00:00:00), +characters (00:00:00), +console (00:00:00), +contain (00:00:00), +container (00:00:00), +cript (00:00:00), +document (00:00:00), +for (00:00:00), +getElementById (00:00:00), +global (00:00:00), +ids (00:00:00), +invalid (00:00:00), +javaScript (00:00:00), +lesson (00:00:00), +like (00:00:00), +log (00:00:00), +my (00:00:00), +myArray (00:00:00), +mynumber (00:00:00), +mystring (00:00:00), +names (00:00:00), +names (00:00:00), +need (00:00:00), +no (00:00:00), +numbers (00:00:00), +opposite (00:00:00), +oppositeboolean (00:00:00), +or (00:00:00), +spaces (00:00:00), +special (00:00:00), +start (00:00:00), +string (00:00:00), +that (00:00:00), +valid (00:00:00), +variables (00:00:00), +with (00:00:00), -&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095), -" (13:05:08.847), -black (13:05:20.120), -brown (13:05:24.043), -; (13:07:10.952), -Charlie (13:07:39.223), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -black (13:11:11.856), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Academy (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Academy (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095) ~0.00, -" (13:05:08.847) ~0.00, -black (13:05:20.120) ~0.80, -brown (13:05:24.043) ~0.80, -; (13:07:10.952), -Charlie (13:07:39.223) ~0.43, -black (13:11:11.856) ~0.80, -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095) ~0.00, -" (13:05:08.847) ~0.00, -black (13:05:20.120) ~0.80, -brown (13:05:24.043) ~0.80, -; (13:07:10.952), -Charlie (13:07:39.223) ~0.43, -black (13:11:11.856) ~0.80, -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Academy (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Academy (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>" (x2), ,, Emnet, First, abbbriviations, anotherdog (x2), karelia (x2), o1 (x3), swtich</t>
+          <t>" (x2), ,, Emnet, First, abbbriviations, anotherdog (x2), academy (x2), o1 (x3), swtich</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
+          <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +Emnet (00:00:00), +First (00:00:00), +abbbriviations (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +academy (00:00:00), +academy (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +swtich (00:00:00), -first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), -Academy (12:35:33.317), -; (12:35:38.458), -Academy (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520)</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-Karelia (12:35:33.317) ~0.86, -; (12:35:38.458), -Karelia (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520) ~0.67, +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
+          <t>-Academy (12:35:33.317) ~0.86, -; (12:35:38.458), -Academy (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -switch (13:35:50.520) ~0.67, +academy (00:00:00), +academy (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +" (00:00:00), +swtich (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" s="4" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>" (x2), ' (x2), Charle, abbreviation, august, friday, getDate, karelia, max, mynumber (x2), orderlist, thursday, tuesday, viewpoint, wednesday, weekend</t>
+          <t>" (x2), ' (x2), Charle, abbreviation, august, friday, getDate, academy, max, mynumber (x2), orderlist, thursday, tuesday, viewpoint, wednesday, weekend</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +Charle (00:00:00), +abbreviation (00:00:00), +august (00:00:00), +friday (00:00:00), +getDate (00:00:00), +karelia (00:00:00), +max (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +orderlist (00:00:00), +thursday (00:00:00), +tuesday (00:00:00), +viewpoint (00:00:00), +wednesday (00:00:00), +weekend (00:00:00), -viewport (12:24:12.738), -abbreviations (12:29:01.416), -ordered (12:31:02.226), -list (12:31:03.447), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:46:59.354), -Max (13:05:08.613), -Charlie (13:07:39.223), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -getDay (13:34:50.180), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693)</t>
+          <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +Charle (00:00:00), +abbreviation (00:00:00), +august (00:00:00), +friday (00:00:00), +getDate (00:00:00), +academy (00:00:00), +max (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +orderlist (00:00:00), +thursday (00:00:00), +tuesday (00:00:00), +viewpoint (00:00:00), +wednesday (00:00:00), +weekend (00:00:00), -viewport (12:24:12.738), -abbreviations (12:29:01.416), -ordered (12:31:02.226), -list (12:31:03.447), -myNumber (12:33:44.402), -myNumber (12:33:59.949), -Academy (12:46:59.354), -Max (13:05:08.613), -Charlie (13:07:39.223), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -getDay (13:34:50.180), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693)</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -Charlie (13:07:39.223) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -getDay (13:34:50.180) ~0.71, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.83, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Academy (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -Charlie (13:07:39.223) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -getDay (13:34:50.180) ~0.71, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.83, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +academy (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
       <c r="Q45" s="4" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Furr, Html, Kareliaa, Lession, defult, year, log*</t>
+          <t>Furr, Html, Academya, Lession, defult, year, log*</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>+Furr (00:00:00), +Html (00:00:00), +Kareliaa (00:00:00), +Lession (00:00:00), +defult (00:00:00), +year (00:00:00), -Lesson (12:24:25.593), -HTML (12:30:43.236), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818), -default (13:37:00.967)</t>
+          <t>+Furr (00:00:00), +Html (00:00:00), +Academya (00:00:00), +Lession (00:00:00), +defult (00:00:00), +year (00:00:00), -Lesson (12:24:25.593), -HTML (12:30:43.236), -Academy (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818), -default (13:37:00.967)</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-Karelia (12:46:59.354) ~0.88, +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077) ~0.75, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818) ~0.80, -default (13:37:00.967) ~0.86, +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
+          <t>-Academy (12:46:59.354) ~0.88, +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077) ~0.75, -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -; (13:25:51.456), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -years (13:31:05.818) ~0.80, -default (13:37:00.967) ~0.86, +Academya (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
         </is>
       </c>
       <c r="Q46" s="4" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>" (x2), Agust, Karelia, Numbers, Viewport, charlie, comsole, cosole, date (x2), intial, karelia, lesson, order</t>
+          <t>" (x2), Agust, Academy, Numbers, Viewport, charlie, comsole, cosole, date (x2), intial, academy, lesson, order</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +Agust (00:00:00), +Karelia (00:00:00), +Numbers (00:00:00), +Viewport (00:00:00), +charlie (00:00:00), +comsole (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +intial (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +order (00:00:00), -viewport (12:24:12.738), -initial (12:24:13.118), -Lesson (12:24:25.593), -/ (12:29:39.313), -ordered (12:31:02.226), -Charlie (13:07:39.223), -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678)</t>
+          <t>+" (00:00:00), +" (00:00:00), +Agust (00:00:00), +Academy (00:00:00), +Numbers (00:00:00), +Viewport (00:00:00), +charlie (00:00:00), +comsole (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +intial (00:00:00), +academy (00:00:00), +lesson (00:00:00), +order (00:00:00), -viewport (12:24:12.738), -initial (12:24:13.118), -Lesson (12:24:25.593), -/ (12:29:39.313), -ordered (12:31:02.226), -Charlie (13:07:39.223), -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Academy (13:29:38.066), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678)</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-Charlie (13:07:39.223) ~0.86, -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Karelia (13:29:38.066) ~0.86, -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
+          <t>-Charlie (13:07:39.223) ~0.86, -console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Academy (13:29:38.066) ~0.86, -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +Academy (00:00:00), +academy (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
         </is>
       </c>
       <c r="Q48" s="4" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>+22 (00:00:00), +Karela (00:00:00), +Lession (00:00:00), +abbreviatios (00:00:00), -Lesson (12:24:25.593), -abbreviations (12:29:01.416), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030), -36 (13:30:50.077)</t>
+          <t>+22 (00:00:00), +Karela (00:00:00), +Lession (00:00:00), +abbreviatios (00:00:00), -Lesson (12:24:25.593), -abbreviations (12:29:01.416), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Academy (13:28:16.030), -36 (13:30:50.077)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030) ~0.86, -36 (13:30:50.077) ~0.00, +Karela (00:00:00), +22 (00:00:00)</t>
+          <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Academy (13:28:16.030) ~0.86, -36 (13:30:50.077) ~0.00, +Karela (00:00:00), +22 (00:00:00)</t>
         </is>
       </c>
       <c r="Q51" s="4" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>", ' (x2), (, ), , (x4), ., 19, 2006, 28, 4, 5, 55, 67 (x2), ; (x2), =, December, Hello (x2), XXX, Years, a, console, const, containter, item, karelia (x3), log, rex</t>
+          <t>", ' (x2), (, ), , (x4), ., 19, 2006, 28, 4, 5, 55, 67 (x2), ; (x2), =, December, Hello (x2), XXX, Years, a, console, const, containter, item, academy (x3), log, rex</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +) (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +. (00:00:00), +19 (00:00:00), +2006 (00:00:00), +28 (00:00:00), +4 (00:00:00), +5 (00:00:00), +55 (00:00:00), +67 (00:00:00), +67 (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +December (00:00:00), +Hello (00:00:00), +Hello (00:00:00), +XXX (00:00:00), +Years (00:00:00), +a (00:00:00), +console (00:00:00), +const (00:00:00), +containter (00:00:00), +item (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +log (00:00:00), +rex (00:00:00), -container (12:30:48.969), -items (12:31:06.206), -25 (12:33:49.617), -2 (12:33:50.650), -; (12:36:56.445), -Karelia (12:46:59.354), -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170), -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030), -! (13:28:16.362), -Karelia (13:28:30.418), -! (13:28:30.583), -" (13:29:31.463), -Karelia (13:29:38.066), -36 (13:30:50.077), -years (13:32:12.609), -; (13:32:15.376), -August (13:33:55.549), -24 (13:33:56.247), -2025 (13:33:58.460)</t>
+          <t>+" (00:00:00), +' (00:00:00), +' (00:00:00), +( (00:00:00), +) (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +. (00:00:00), +19 (00:00:00), +2006 (00:00:00), +28 (00:00:00), +4 (00:00:00), +5 (00:00:00), +55 (00:00:00), +67 (00:00:00), +67 (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +December (00:00:00), +Hello (00:00:00), +Hello (00:00:00), +XXX (00:00:00), +Years (00:00:00), +a (00:00:00), +console (00:00:00), +const (00:00:00), +containter (00:00:00), +item (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +log (00:00:00), +rex (00:00:00), -container (12:30:48.969), -items (12:31:06.206), -25 (12:33:49.617), -2 (12:33:50.650), -; (12:36:56.445), -Academy (12:46:59.354), -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170), -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Academy (13:28:16.030), -! (13:28:16.362), -Academy (13:28:30.418), -! (13:28:30.583), -" (13:29:31.463), -Academy (13:29:38.066), -36 (13:30:50.077), -years (13:32:12.609), -; (13:32:15.376), -August (13:33:55.549), -24 (13:33:56.247), -2025 (13:33:58.460)</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>-25 (12:33:49.617) ~0.00, -2 (12:33:50.650) ~0.00, -; (12:36:56.445), -Karelia (12:46:59.354) ~0.00, -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170) ~0.67, -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -" (13:29:31.463) ~0.00, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:32:12.609) ~0.80, -; (13:32:15.376), -August (13:33:55.549) ~0.00, -24 (13:33:56.247) ~0.50, -2025 (13:33:58.460) ~0.50, +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
+          <t>-25 (12:33:49.617) ~0.00, -2 (12:33:50.650) ~0.00, -; (12:36:56.445), -Academy (12:46:59.354) ~0.00, -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170) ~0.67, -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Academy (13:28:16.030) ~0.86, -! (13:28:16.362), -Academy (13:28:30.418) ~0.86, -! (13:28:30.583), -" (13:29:31.463) ~0.00, -Academy (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:32:12.609) ~0.80, -; (13:32:15.376), -August (13:33:55.549) ~0.00, -24 (13:33:56.247) ~0.50, -2025 (13:33:58.460) ~0.50, +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +academy (00:00:00), +academy (00:00:00), +' (00:00:00), +academy (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
         </is>
       </c>
       <c r="Q56" s="4" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>" (x2), 1 (x4), Console, SomeDate, abbreviation, karelia, toady</t>
+          <t>" (x2), 1 (x4), Console, SomeDate, abbreviation, academy, toady</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +Console (00:00:00), +SomeDate (00:00:00), +abbreviation (00:00:00), +karelia (00:00:00), +toady (00:00:00), -abbreviations (12:29:01.416), -Karelia (12:46:59.354), -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097)</t>
+          <t>+" (00:00:00), +" (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +Console (00:00:00), +SomeDate (00:00:00), +abbreviation (00:00:00), +academy (00:00:00), +toady (00:00:00), -abbreviations (12:29:01.416), -Academy (12:46:59.354), -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097)</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-Karelia (12:46:59.354) ~0.86, -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +karelia (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
+          <t>-Academy (12:46:59.354) ~0.86, -= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +academy (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" s="4" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>" (x2), ( (x2), ) (x2), ,, . (x2), 142, ; (x2), Console, First, Math, Ordered, a, appendchild, b, connstmyString, consloe, console, java, karelia (x4), lesson, log, max, mynumber (x2), pow, script, tab, year</t>
+          <t>" (x2), ( (x2), ) (x2), ,, . (x2), 142, ; (x2), Console, First, Math, Ordered, a, appendchild, b, connstmyString, consloe, console, java, academy (x4), lesson, log, max, mynumber (x2), pow, script, tab, year</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +. (00:00:00), +. (00:00:00), +142 (00:00:00), +; (00:00:00), +; (00:00:00), +Console (00:00:00), +First (00:00:00), +Math (00:00:00), +Ordered (00:00:00), +a (00:00:00), +appendchild (00:00:00), +b (00:00:00), +connstmyString (00:00:00), +consloe (00:00:00), +console (00:00:00), +java (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +log (00:00:00), +max (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +pow (00:00:00), +script (00:00:00), +tab (00:00:00), +year (00:00:00), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -first (12:28:57.481), -! (12:30:40.873), -ordered (12:31:02.226), -Tab (12:31:12.499), -myNumber (12:33:44.402), -console (12:33:56.141), -myNumber (12:33:59.949), -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317), -! (12:42:04.755), -42 (12:42:11.528), -console (12:43:10.202), -Karelia (12:46:59.354), -Max (13:05:08.613), -appendChild (13:13:30.342), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -Karelia (13:29:38.066), -years (13:32:12.609), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+          <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +. (00:00:00), +. (00:00:00), +142 (00:00:00), +; (00:00:00), +; (00:00:00), +Console (00:00:00), +First (00:00:00), +Math (00:00:00), +Ordered (00:00:00), +a (00:00:00), +appendchild (00:00:00), +b (00:00:00), +connstmyString (00:00:00), +consloe (00:00:00), +console (00:00:00), +java (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +lesson (00:00:00), +log (00:00:00), +max (00:00:00), +mynumber (00:00:00), +mynumber (00:00:00), +pow (00:00:00), +script (00:00:00), +tab (00:00:00), +year (00:00:00), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -first (12:28:57.481), -! (12:30:40.873), -ordered (12:31:02.226), -Tab (12:31:12.499), -myNumber (12:33:44.402), -console (12:33:56.141), -myNumber (12:33:59.949), -const (12:35:25.644), -myString (12:35:27.676), -Academy (12:35:33.317), -! (12:42:04.755), -42 (12:42:11.528), -console (12:43:10.202), -Academy (12:46:59.354), -Max (13:05:08.613), -appendChild (13:13:30.342), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250), -Academy (13:28:30.418), -' (13:28:30.981), -Academy (13:29:38.066), -years (13:32:12.609), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402) ~0.88, -console (12:33:56.141) ~0.71, -myNumber (12:33:59.949) ~0.88, -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317) ~0.86, -! (12:42:04.755), -42 (12:42:11.528) ~0.67, -console (12:43:10.202) ~0.86, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -appendChild (13:13:30.342) ~0.91, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -Karelia (13:29:38.066) ~0.86, -years (13:32:12.609) ~0.80, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00), +; (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -console (12:33:56.141) ~0.71, -myNumber (12:33:59.949) ~0.88, -const (12:35:25.644), -myString (12:35:27.676), -Academy (12:35:33.317) ~0.86, -! (12:42:04.755), -42 (12:42:11.528) ~0.67, -console (12:43:10.202) ~0.86, -Academy (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -appendChild (13:13:30.342) ~0.91, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250) ~0.00, -Academy (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -Academy (13:29:38.066) ~0.86, -years (13:32:12.609) ~0.80, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +academy (00:00:00), +142 (00:00:00), +Console (00:00:00), +academy (00:00:00), +max (00:00:00), +appendchild (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +" (00:00:00), +academy (00:00:00), +" (00:00:00), +academy (00:00:00), +year (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q61" s="4" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>" (x3), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, karelia, max, muBoolean, my, orderd, t (x3), title, we, welcome (x3), Document*, log*</t>
+          <t>" (x3), #, ,, /, 1 (x2), &lt;, &gt; (x2), Radufromfinland, Tu, abbrevetion, agust, breake (x3), charlie, getDate, gog, html, i (x2), in, itemes, javascriptlesson, academy, max, muBoolean, my, orderd, t (x3), title, we, welcome (x3), Document*, log*</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +karelia (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
+          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +# (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Radufromfinland (00:00:00), +Tu (00:00:00), +abbrevetion (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +charlie (00:00:00), +getDate (00:00:00), +gog (00:00:00), +html (00:00:00), +i (00:00:00), +i (00:00:00), +in (00:00:00), +itemes (00:00:00), +javascriptlesson (00:00:00), +academy (00:00:00), +max (00:00:00), +muBoolean (00:00:00), +my (00:00:00), +orderd (00:00:00), +t (00:00:00), +t (00:00:00), +t (00:00:00), +title (00:00:00), +we (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Academy (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -radufromfinland (13:09:39.343), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Karelia (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -to (13:29:35.300) ~0.50, -" (13:29:36.010), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970) ~0.00, -Wednesday (13:36:38.686) ~0.11, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
+          <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Academy (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -Welcome (13:29:34.675) ~0.86, -to (13:29:35.300) ~0.50, -" (13:29:36.010), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970) ~0.00, -Wednesday (13:36:38.686) ~0.11, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +academy (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +" (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" s="4" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>", , (x2), / (x3), 22, Console, MAX, aage, anoherDog, karelia (x2), lesson, muBoolean, muNumber, weelend, } (x5), ´ (x2)</t>
+          <t>", , (x2), / (x3), 22, Console, MAX, aage, anoherDog, academy (x2), lesson, muBoolean, muNumber, weelend, } (x5), ´ (x2)</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +, (00:00:00), +, (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +22 (00:00:00), +Console (00:00:00), +MAX (00:00:00), +aage (00:00:00), +anoherDog (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +lesson (00:00:00), +muBoolean (00:00:00), +muNumber (00:00:00), +weelend (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +´ (00:00:00), +´ (00:00:00), -Lesson (12:24:25.593), -! (12:30:40.873), -myNumber (12:33:44.402), -myBoolean (12:36:27.967), -Karelia (12:46:59.354), -. (12:58:07.899), -; (13:02:35.373), -Max (13:05:08.613), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -age (13:30:48.674), -36 (13:30:50.077), -` (13:32:14.220), -; (13:32:15.376), -console (13:34:46.231), -} (13:35:58.376), -Weekend (13:37:10.693), -; (13:38:10.869)</t>
+          <t>+" (00:00:00), +, (00:00:00), +, (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +22 (00:00:00), +Console (00:00:00), +MAX (00:00:00), +aage (00:00:00), +anoherDog (00:00:00), +academy (00:00:00), +academy (00:00:00), +lesson (00:00:00), +muBoolean (00:00:00), +muNumber (00:00:00), +weelend (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +´ (00:00:00), +´ (00:00:00), -Lesson (12:24:25.593), -! (12:30:40.873), -myNumber (12:33:44.402), -myBoolean (12:36:27.967), -Academy (12:46:59.354), -. (12:58:07.899), -; (13:02:35.373), -Max (13:05:08.613), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -Academy (13:29:38.066), -\ (13:29:38.349), -age (13:30:48.674), -36 (13:30:50.077), -` (13:32:14.220), -; (13:32:15.376), -console (13:34:46.231), -} (13:35:58.376), -Weekend (13:37:10.693), -; (13:38:10.869)</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -Karelia (12:46:59.354) ~0.86, -. (12:58:07.899) ~0.00, -; (13:02:35.373) ~0.00, -Max (13:05:08.613) ~0.33, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010), -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -36 (13:30:50.077) ~0.00, -` (13:32:14.220) ~0.00, -; (13:32:15.376), -console (13:34:46.231) ~0.86, -} (13:35:58.376), -Weekend (13:37:10.693) ~0.71, -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -Academy (12:46:59.354) ~0.86, -. (12:58:07.899) ~0.00, -; (13:02:35.373) ~0.00, -Max (13:05:08.613) ~0.33, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010), -Academy (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -36 (13:30:50.077) ~0.00, -` (13:32:14.220) ~0.00, -; (13:32:15.376), -console (13:34:46.231) ~0.86, -} (13:35:58.376), -Weekend (13:37:10.693) ~0.71, -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +academy (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +academy (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" s="4" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>22, Karelia, karelia, studt, todat, viewpoint, year</t>
+          <t>22, Academy, academy, studt, todat, viewpoint, year</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>+22 (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +studt (00:00:00), +todat (00:00:00), +viewpoint (00:00:00), +year (00:00:00), -viewport (12:24:12.738), -study (12:35:31.258), -Karelia (12:35:33.317), -36 (13:30:50.077), -years (13:31:05.818), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+          <t>+22 (00:00:00), +Academy (00:00:00), +academy (00:00:00), +studt (00:00:00), +todat (00:00:00), +viewpoint (00:00:00), +year (00:00:00), -viewport (12:24:12.738), -study (12:35:31.258), -Academy (12:35:33.317), -36 (13:30:50.077), -years (13:31:05.818), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
       <c r="M72" t="n">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-study (12:35:31.258) ~0.80, -Karelia (12:35:33.317) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:31:05.818) ~0.80, -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
+          <t>-study (12:35:31.258) ~0.80, -Academy (12:35:33.317) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:31:05.818) ~0.80, -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +academy (00:00:00), +Academy (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
         </is>
       </c>
       <c r="Q72" s="4" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>", / (x2), ;, Boolean (x2), HTMl, browen, charlie, friday, getday, karelia (x5), let, math (x3), max, monday, my, myboolean (x2), myboolen, myoolean, mystring (x2), number, oppositeboolean, port, saturday, tab, thursday, today, tuesday, underfined, view, yeasrs, log*</t>
+          <t>", / (x2), ;, Boolean (x2), HTMl, browen, charlie, friday, getday, academy (x5), let, math (x3), max, monday, my, myboolean (x2), myboolen, myoolean, mystring (x2), number, oppositeboolean, port, saturday, tab, thursday, today, tuesday, underfined, view, yeasrs, log*</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +HTMl (00:00:00), +browen (00:00:00), +charlie (00:00:00), +friday (00:00:00), +getday (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +saturday (00:00:00), +tab (00:00:00), +thursday (00:00:00), +today (00:00:00), +tuesday (00:00:00), +underfined (00:00:00), +view (00:00:00), +yeasrs (00:00:00), -viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), -myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
+          <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +HTMl (00:00:00), +browen (00:00:00), +charlie (00:00:00), +friday (00:00:00), +getday (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +academy (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +max (00:00:00), +monday (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +mystring (00:00:00), +mystring (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +saturday (00:00:00), +tab (00:00:00), +thursday (00:00:00), +today (00:00:00), +tuesday (00:00:00), +underfined (00:00:00), +view (00:00:00), +yeasrs (00:00:00), -viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), -myString (12:35:27.676), -Academy (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Academy (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Academy (13:28:16.030), -' (13:28:26.250), -Academy (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759), -Academy (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
         </is>
       </c>
       <c r="M75" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108), -myBoolean (12:41:00.416) ~0.89, -; (12:41:04.494), -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, -Karelia (12:46:59.354) ~0.86, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613) ~0.67, -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -; (13:26:07.158), -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759) ~0.00, -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -years (13:32:12.609) ~0.83, -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019) ~0.25, -getDay (13:35:54.315) ~0.83, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.44, -Thursday (13:36:45.577) ~0.50, -Friday (13:36:53.097) ~0.38, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +today (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
+          <t>-myString (12:35:27.676) ~0.88, -Academy (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108), -myBoolean (12:41:00.416) ~0.89, -; (12:41:04.494), -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, -Academy (12:46:59.354) ~0.86, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613) ~0.67, -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -; (13:26:07.158), -Academy (13:28:16.030) ~0.86, -' (13:28:26.250) ~0.00, -Academy (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759) ~0.00, -Academy (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -years (13:32:12.609) ~0.83, -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019) ~0.25, -getDay (13:35:54.315) ~0.83, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.44, -Thursday (13:36:45.577) ~0.50, -Friday (13:36:53.097) ~0.38, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +mystring (00:00:00), +academy (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +academy (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +academy (00:00:00), +" (00:00:00), +academy (00:00:00), +/ (00:00:00), +academy (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +today (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>+21 (00:00:00), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), -ABC (12:42:20.731), -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354), -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077), -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077), -; (13:31:07.806), -; (13:32:15.376)</t>
+          <t>+21 (00:00:00), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), -ABC (12:42:20.731), -; (12:42:36.696), -; (12:43:22.016), -Academy (12:46:59.354), -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077), -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077), -; (13:31:07.806), -; (13:32:15.376)</t>
         </is>
       </c>
       <c r="M82" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>-ABC (12:42:20.731) ~0.00, -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354) ~0.00, -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077) ~0.75, -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
+          <t>-ABC (12:42:20.731) ~0.00, -; (12:42:36.696), -; (12:43:22.016), -Academy (12:46:59.354) ~0.00, -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077) ~0.75, -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
         </is>
       </c>
       <c r="Q82" s="4" t="inlineStr">
